--- a/uploads/transfer.xlsx
+++ b/uploads/transfer.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251031\eksport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\Eksport\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="163">
   <si>
     <t>nomor_request</t>
   </si>
@@ -66,100 +66,121 @@
     <t>ex: angka</t>
   </si>
   <si>
-    <t>2526ACH25000103</t>
-  </si>
-  <si>
-    <t>25ASB25017124</t>
+    <t>2826ACH25000015</t>
+  </si>
+  <si>
+    <t>25ASB24015854</t>
+  </si>
+  <si>
+    <t>PUSAT (PIUTANG)</t>
+  </si>
+  <si>
+    <t>BEKASI</t>
+  </si>
+  <si>
+    <t>POT RETUR TRANSMART PEMBAYARAN 30.05.25</t>
+  </si>
+  <si>
+    <t>Intransit</t>
+  </si>
+  <si>
+    <t>OUTSTANDING</t>
+  </si>
+  <si>
+    <t>2526ACH25000108</t>
+  </si>
+  <si>
+    <t>25ASB25017920</t>
   </si>
   <si>
     <t>TANGERANG</t>
   </si>
   <si>
-    <t>BEKASI</t>
-  </si>
-  <si>
-    <t>TF MITRA GADING</t>
-  </si>
-  <si>
-    <t>Intransit</t>
-  </si>
-  <si>
-    <t>OUTSTANDING</t>
-  </si>
-  <si>
-    <t>25ASB25017125</t>
-  </si>
-  <si>
-    <t>25ASB25017150</t>
-  </si>
-  <si>
-    <t>25ASB25017193</t>
-  </si>
-  <si>
-    <t>25ASB25017214</t>
-  </si>
-  <si>
-    <t>2526ACH25000104</t>
-  </si>
-  <si>
-    <t>25ASB25017318</t>
-  </si>
-  <si>
-    <t>TF MITRA KELUARGA KALIDERES</t>
-  </si>
-  <si>
-    <t>25ASB25017319</t>
-  </si>
-  <si>
-    <t>25ASB25017320</t>
-  </si>
-  <si>
-    <t>25ASB25017341</t>
-  </si>
-  <si>
-    <t>25ASB25017342</t>
-  </si>
-  <si>
-    <t>25ASB25017343</t>
-  </si>
-  <si>
-    <t>25ASB25017344</t>
-  </si>
-  <si>
-    <t>25ASB25017358</t>
-  </si>
-  <si>
-    <t>25ASB25017359</t>
-  </si>
-  <si>
-    <t>25ASB25017396</t>
-  </si>
-  <si>
-    <t>25ASB25017488</t>
-  </si>
-  <si>
-    <t>25ASB25017489</t>
-  </si>
-  <si>
-    <t>25ASB25017490</t>
-  </si>
-  <si>
-    <t>25ASB25017491</t>
-  </si>
-  <si>
-    <t>25ASB25017588</t>
-  </si>
-  <si>
-    <t>2526BCH25000037</t>
-  </si>
-  <si>
-    <t>25BSB25001468</t>
-  </si>
-  <si>
-    <t>2726ACH25000072</t>
-  </si>
-  <si>
-    <t>27ASB25018473</t>
+    <t>TF MITRA KELUARGA GADING SERPONG</t>
+  </si>
+  <si>
+    <t>2526ACH25000107</t>
+  </si>
+  <si>
+    <t>25ASB25017934</t>
+  </si>
+  <si>
+    <t>TF RSU MITRA KALIDERES</t>
+  </si>
+  <si>
+    <t>25ASB25017970</t>
+  </si>
+  <si>
+    <t>25ASB25017971</t>
+  </si>
+  <si>
+    <t>25ASB25017994</t>
+  </si>
+  <si>
+    <t>25ASB25017995</t>
+  </si>
+  <si>
+    <t>25ASB25017996</t>
+  </si>
+  <si>
+    <t>25ASB25018077</t>
+  </si>
+  <si>
+    <t>25ASB25018110</t>
+  </si>
+  <si>
+    <t>25ASB25018190</t>
+  </si>
+  <si>
+    <t>25ASB25018235</t>
+  </si>
+  <si>
+    <t>25ASB25018247</t>
+  </si>
+  <si>
+    <t>2526BCH25000039</t>
+  </si>
+  <si>
+    <t>25BSB25001513</t>
+  </si>
+  <si>
+    <t>TF MITRA GADING SERPONG</t>
+  </si>
+  <si>
+    <t>26ASB24021414</t>
+  </si>
+  <si>
+    <t>26ASB24022295</t>
+  </si>
+  <si>
+    <t>2826ACH25000016</t>
+  </si>
+  <si>
+    <t>26ASB25020250</t>
+  </si>
+  <si>
+    <t>POT RETUR WATSON BKS KPO 16.10.2025</t>
+  </si>
+  <si>
+    <t>26ASB25020251</t>
+  </si>
+  <si>
+    <t>2826ACH25000017</t>
+  </si>
+  <si>
+    <t>26ASB25021228</t>
+  </si>
+  <si>
+    <t>POT RETUR WATSON BKS KPO 27.10.2025</t>
+  </si>
+  <si>
+    <t>27ASB25014375</t>
+  </si>
+  <si>
+    <t>2726ACH25000076</t>
+  </si>
+  <si>
+    <t>27ASB25019936</t>
   </si>
   <si>
     <t>JAKARTA SELATAN</t>
@@ -168,262 +189,307 @@
     <t>TUKAR FAKTUR DI BKS</t>
   </si>
   <si>
-    <t>27ASB25018758</t>
-  </si>
-  <si>
-    <t>27ASB25018759</t>
-  </si>
-  <si>
-    <t>27ASB25018760</t>
-  </si>
-  <si>
-    <t>27ASB25018761</t>
-  </si>
-  <si>
-    <t>27ASB25018763</t>
-  </si>
-  <si>
-    <t>27ASB25018764</t>
-  </si>
-  <si>
-    <t>27ASB25018765</t>
-  </si>
-  <si>
-    <t>27ASB25018767</t>
-  </si>
-  <si>
-    <t>27ASB25018901</t>
-  </si>
-  <si>
-    <t>27ASB25018981</t>
-  </si>
-  <si>
-    <t>27ASB25018982</t>
-  </si>
-  <si>
-    <t>27ASB25018983</t>
-  </si>
-  <si>
-    <t>27ASB25018984</t>
-  </si>
-  <si>
-    <t>27ASB25018985</t>
-  </si>
-  <si>
-    <t>27ASB25019097</t>
-  </si>
-  <si>
-    <t>27ASB25019137</t>
-  </si>
-  <si>
-    <t>27ASB25019139</t>
-  </si>
-  <si>
-    <t>27ASB25019141</t>
-  </si>
-  <si>
-    <t>27ASB25019142</t>
-  </si>
-  <si>
-    <t>27ASB25019198</t>
-  </si>
-  <si>
-    <t>27ASB25019201</t>
-  </si>
-  <si>
-    <t>27ASB25019209</t>
-  </si>
-  <si>
-    <t>27ASB25019210</t>
-  </si>
-  <si>
-    <t>27ASB25019211</t>
-  </si>
-  <si>
-    <t>27ASB25019212</t>
-  </si>
-  <si>
-    <t>27ASB25019242</t>
-  </si>
-  <si>
-    <t>2726ACH25000073</t>
-  </si>
-  <si>
-    <t>27ASB25019307</t>
+    <t>27ASB25019937</t>
+  </si>
+  <si>
+    <t>27ASB25019949</t>
+  </si>
+  <si>
+    <t>27ASB25019950</t>
+  </si>
+  <si>
+    <t>27ASB25019951</t>
+  </si>
+  <si>
+    <t>27ASB25019952</t>
+  </si>
+  <si>
+    <t>27ASB25019953</t>
+  </si>
+  <si>
+    <t>27ASB25019954</t>
+  </si>
+  <si>
+    <t>27ASB25019955</t>
+  </si>
+  <si>
+    <t>27ASB25020020</t>
+  </si>
+  <si>
+    <t>27ASB25020128</t>
+  </si>
+  <si>
+    <t>27ASB25020129</t>
+  </si>
+  <si>
+    <t>27ASB25020216</t>
+  </si>
+  <si>
+    <t>27ASB25020217</t>
+  </si>
+  <si>
+    <t>27ASB25020218</t>
+  </si>
+  <si>
+    <t>27ASB25020219</t>
+  </si>
+  <si>
+    <t>27ASB25020220</t>
+  </si>
+  <si>
+    <t>27ASB25020221</t>
+  </si>
+  <si>
+    <t>27ASB25020222</t>
+  </si>
+  <si>
+    <t>27ASB25020253</t>
+  </si>
+  <si>
+    <t>2726ACH25000075</t>
+  </si>
+  <si>
+    <t>27ASB25020299</t>
   </si>
   <si>
     <t>NAGA SWALAYAN</t>
   </si>
   <si>
-    <t>27ASB25019308</t>
-  </si>
-  <si>
-    <t>2807ACH25000090</t>
+    <t>27ASB25020314</t>
+  </si>
+  <si>
+    <t>27ASB25020419</t>
+  </si>
+  <si>
+    <t>27ASB25020428</t>
+  </si>
+  <si>
+    <t>27ASB25020451</t>
+  </si>
+  <si>
+    <t>27ASB25020452</t>
+  </si>
+  <si>
+    <t>27ASB25020453</t>
+  </si>
+  <si>
+    <t>27ASB25020454</t>
+  </si>
+  <si>
+    <t>27ASB25020455</t>
+  </si>
+  <si>
+    <t>2726BCH25000023</t>
+  </si>
+  <si>
+    <t>27BSB25000643</t>
+  </si>
+  <si>
+    <t>27BSB25000650</t>
+  </si>
+  <si>
+    <t>1801BCH25000001</t>
+  </si>
+  <si>
+    <t>18BSB25000214</t>
+  </si>
+  <si>
+    <t>PUSAT 79</t>
+  </si>
+  <si>
+    <t>CIREBON</t>
+  </si>
+  <si>
+    <t>KP.CIREBON</t>
+  </si>
+  <si>
+    <t>2807ACH25000091</t>
   </si>
   <si>
     <t>07ASB24028161</t>
   </si>
   <si>
-    <t>PUSAT (PIUTANG)</t>
-  </si>
-  <si>
     <t>JAKARTA PUSAT</t>
   </si>
   <si>
-    <t>PENGEMBALIAN OUTSTANDING PIUTANG JAKPUS</t>
-  </si>
-  <si>
-    <t>2507ACH25000038</t>
-  </si>
-  <si>
-    <t>25ASB25016530</t>
+    <t>PENGEMBALIAN PIUTANG JAKPUS</t>
+  </si>
+  <si>
+    <t>2707ACH25000073</t>
+  </si>
+  <si>
+    <t>07ASB25034549</t>
+  </si>
+  <si>
+    <t>BRAWIJAYA SDH TUKAR</t>
+  </si>
+  <si>
+    <t>07ASB25034824</t>
+  </si>
+  <si>
+    <t>07ASB25034950</t>
+  </si>
+  <si>
+    <t>07ASB25034968</t>
+  </si>
+  <si>
+    <t>07ASB25035316</t>
+  </si>
+  <si>
+    <t>2807ACH25000092</t>
+  </si>
+  <si>
+    <t>25ASB25014626</t>
+  </si>
+  <si>
+    <t>PEMBAYARAN DI JAKPUS KPO 12.11.2025</t>
+  </si>
+  <si>
+    <t>2507ACH25000042</t>
+  </si>
+  <si>
+    <t>25ASB25017826</t>
   </si>
   <si>
     <t>TF DI JAKPUS</t>
   </si>
   <si>
-    <t>2507ACH25000040</t>
-  </si>
-  <si>
-    <t>25ASB25017112</t>
-  </si>
-  <si>
-    <t>ERA CARING TUKAR FAKTUR DI JAKPUS</t>
-  </si>
-  <si>
-    <t>25ASB25017210</t>
-  </si>
-  <si>
-    <t>2800ACH25000079</t>
-  </si>
-  <si>
-    <t>28ACB25000113-1</t>
+    <t>25ASB25017911</t>
+  </si>
+  <si>
+    <t>25ASB25018023</t>
+  </si>
+  <si>
+    <t>25ASB25018254</t>
+  </si>
+  <si>
+    <t>2507ACH25000043</t>
+  </si>
+  <si>
+    <t>25ASG25000380</t>
+  </si>
+  <si>
+    <t>CN ERA CARING</t>
+  </si>
+  <si>
+    <t>DEPOSIT</t>
+  </si>
+  <si>
+    <t>25ASG25000417</t>
+  </si>
+  <si>
+    <t>27ASB25015642</t>
+  </si>
+  <si>
+    <t>2707ACH25000071</t>
+  </si>
+  <si>
+    <t>27ASB25017192</t>
+  </si>
+  <si>
+    <t>HOKKY BERSAMA</t>
+  </si>
+  <si>
+    <t>2707ACH25000072</t>
+  </si>
+  <si>
+    <t>27ASB25020038</t>
+  </si>
+  <si>
+    <t>TUKAR FAKTUR DI JAKPUS</t>
+  </si>
+  <si>
+    <t>0700ACH25000059</t>
+  </si>
+  <si>
+    <t>07ASB25035953</t>
   </si>
   <si>
     <t>KANTOR PUSAT</t>
   </si>
   <si>
-    <t>UM PPH 23 TIP TOP KUINTANSI NO 011644</t>
-  </si>
-  <si>
-    <t>DEPOSIT</t>
-  </si>
-  <si>
-    <t>0728ACH25000170</t>
-  </si>
-  <si>
-    <t>07ASB25034438</t>
-  </si>
-  <si>
-    <t>TF DI PUSAT</t>
-  </si>
-  <si>
-    <t>2528ACH25000083</t>
-  </si>
-  <si>
-    <t>25ASB25017063</t>
-  </si>
-  <si>
-    <t>TUKAR FAKTUR DI PUSAT</t>
-  </si>
-  <si>
-    <t>25ASB25017237</t>
-  </si>
-  <si>
-    <t>25ASB25017326</t>
-  </si>
-  <si>
-    <t>25ASB25017439</t>
-  </si>
-  <si>
-    <t>2728ACH25000048</t>
-  </si>
-  <si>
-    <t>27ASB25018912</t>
-  </si>
-  <si>
-    <t>TIPTOP, GELAEL, FOODHALL, &amp; WATSONS</t>
-  </si>
-  <si>
-    <t>27ASB25019114</t>
-  </si>
-  <si>
-    <t>27ASB25019164</t>
-  </si>
-  <si>
-    <t>27ASB25019297</t>
-  </si>
-  <si>
-    <t>27ASB25019462</t>
-  </si>
-  <si>
-    <t>0521ACH25000027</t>
-  </si>
-  <si>
-    <t>05ASB25010683</t>
-  </si>
-  <si>
-    <t>PALEMBANG</t>
-  </si>
-  <si>
-    <t>PUSAT 21</t>
-  </si>
-  <si>
-    <t>PENGALIHAN PIUTANG SISA PPN BATAL</t>
-  </si>
-  <si>
-    <t>05ASB25011052</t>
-  </si>
-  <si>
-    <t>0821ACH25000047</t>
-  </si>
-  <si>
-    <t>08ACB24002347-1</t>
-  </si>
-  <si>
-    <t>BOGOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PENGALIHAN OUTSTANDING MINUS </t>
-  </si>
-  <si>
-    <t>2725ACH25000051</t>
-  </si>
-  <si>
-    <t>27ASB25019384</t>
+    <t>POT RAFRAKSI</t>
+  </si>
+  <si>
+    <t>1328ACH25000007</t>
+  </si>
+  <si>
+    <t>13ASB25016823</t>
+  </si>
+  <si>
+    <t>YOGYAKARTA</t>
+  </si>
+  <si>
+    <t>PENGALIHAN PIUTANG WATSON GALERIA</t>
+  </si>
+  <si>
+    <t>2728ACH25000050</t>
+  </si>
+  <si>
+    <t>27ASB25019812</t>
+  </si>
+  <si>
+    <t>TIPTOP, GRANDLUCKY, WATSONS</t>
+  </si>
+  <si>
+    <t>27ASB25020081</t>
+  </si>
+  <si>
+    <t>27ASB25020087</t>
+  </si>
+  <si>
+    <t>27ASB25020089</t>
+  </si>
+  <si>
+    <t>27ASB25020092</t>
+  </si>
+  <si>
+    <t>27ASB25020095</t>
+  </si>
+  <si>
+    <t>27ASB25020143</t>
+  </si>
+  <si>
+    <t>27ASB25020179</t>
+  </si>
+  <si>
+    <t>27ASB25020284</t>
+  </si>
+  <si>
+    <t>27ASB25020285</t>
+  </si>
+  <si>
+    <t>27ASB25020316</t>
+  </si>
+  <si>
+    <t>2725ACH25000054</t>
+  </si>
+  <si>
+    <t>25ASB25016769</t>
+  </si>
+  <si>
+    <t>25ASB25017546</t>
+  </si>
+  <si>
+    <t>2725ACH25000053</t>
+  </si>
+  <si>
+    <t>27ASB25020265</t>
   </si>
   <si>
     <t>TUKAR FAKTUR DI TGR</t>
   </si>
   <si>
-    <t>1113ACH25000009</t>
-  </si>
-  <si>
-    <t>11ASB25030322</t>
-  </si>
-  <si>
-    <t>SEMARANG</t>
-  </si>
-  <si>
-    <t>YOGYAKARTA</t>
-  </si>
-  <si>
-    <t>TITIP FAKTUR KF CABANG PURWOKERTO</t>
-  </si>
-  <si>
-    <t>11ASB25030323</t>
-  </si>
-  <si>
-    <t>11ASB25030324</t>
-  </si>
-  <si>
-    <t>11ASB25030325</t>
-  </si>
-  <si>
-    <t>1213ACH25000015</t>
-  </si>
-  <si>
-    <t>12ASB25021305</t>
+    <t>2725ACH25000055</t>
+  </si>
+  <si>
+    <t>27ASB25020635</t>
+  </si>
+  <si>
+    <t>1213ACH25000016</t>
+  </si>
+  <si>
+    <t>12ASB25021890</t>
   </si>
   <si>
     <t>SOLO</t>
@@ -432,7 +498,16 @@
     <t/>
   </si>
   <si>
-    <t>12ASB25021365</t>
+    <t>12ASB25022059</t>
+  </si>
+  <si>
+    <t>12ASB25022087</t>
+  </si>
+  <si>
+    <t>12ASB25022431</t>
+  </si>
+  <si>
+    <t>12ASB25022464</t>
   </si>
 </sst>
 </file>
@@ -708,7 +783,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J93"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -797,7 +872,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="4">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>20</v>
@@ -806,30 +881,30 @@
         <v>21</v>
       </c>
       <c r="I4" s="3">
-        <v>461205</v>
+        <v>1078388</v>
       </c>
       <c r="J4" s="3">
-        <v>461205</v>
+        <v>37677</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F5" s="4">
-        <v>45959</v>
+        <v>45973</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>20</v>
@@ -838,30 +913,30 @@
         <v>21</v>
       </c>
       <c r="I5" s="3">
-        <v>1842683</v>
+        <v>126540</v>
       </c>
       <c r="J5" s="3">
-        <v>1842683</v>
+        <v>126540</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F6" s="4">
-        <v>45959</v>
+        <v>45972</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>20</v>
@@ -870,30 +945,30 @@
         <v>21</v>
       </c>
       <c r="I6" s="3">
-        <v>56943</v>
+        <v>685980</v>
       </c>
       <c r="J6" s="3">
-        <v>56943</v>
+        <v>685980</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F7" s="4">
-        <v>45959</v>
+        <v>45972</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>20</v>
@@ -902,30 +977,30 @@
         <v>21</v>
       </c>
       <c r="I7" s="3">
-        <v>738150</v>
+        <v>947995</v>
       </c>
       <c r="J7" s="3">
-        <v>738150</v>
+        <v>947995</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F8" s="4">
-        <v>45959</v>
+        <v>45972</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>20</v>
@@ -934,30 +1009,30 @@
         <v>21</v>
       </c>
       <c r="I8" s="3">
-        <v>337440</v>
+        <v>1804860</v>
       </c>
       <c r="J8" s="3">
-        <v>337440</v>
+        <v>1804860</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F9" s="4">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -966,30 +1041,30 @@
         <v>21</v>
       </c>
       <c r="I9" s="3">
-        <v>4772605</v>
+        <v>1883670</v>
       </c>
       <c r="J9" s="3">
-        <v>4772605</v>
+        <v>1883670</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" s="4">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>20</v>
@@ -998,30 +1073,30 @@
         <v>21</v>
       </c>
       <c r="I10" s="3">
-        <v>3428568</v>
+        <v>1638082</v>
       </c>
       <c r="J10" s="3">
-        <v>3428568</v>
+        <v>1638082</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F11" s="4">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>20</v>
@@ -1030,30 +1105,30 @@
         <v>21</v>
       </c>
       <c r="I11" s="3">
-        <v>971250</v>
+        <v>1103284</v>
       </c>
       <c r="J11" s="3">
-        <v>971250</v>
+        <v>1103284</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F12" s="4">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>20</v>
@@ -1062,30 +1137,30 @@
         <v>21</v>
       </c>
       <c r="I12" s="3">
-        <v>284715</v>
+        <v>471599</v>
       </c>
       <c r="J12" s="3">
-        <v>284715</v>
+        <v>471599</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F13" s="4">
-        <v>45959</v>
+        <v>45972</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>20</v>
@@ -1094,30 +1169,30 @@
         <v>21</v>
       </c>
       <c r="I13" s="3">
-        <v>1694914</v>
+        <v>143856</v>
       </c>
       <c r="J13" s="3">
-        <v>1694914</v>
+        <v>143856</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F14" s="4">
-        <v>45959</v>
+        <v>45973</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>20</v>
@@ -1126,30 +1201,30 @@
         <v>21</v>
       </c>
       <c r="I14" s="3">
-        <v>604395</v>
+        <v>2664000</v>
       </c>
       <c r="J14" s="3">
-        <v>604395</v>
+        <v>2664000</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F15" s="4">
-        <v>45959</v>
+        <v>45973</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>20</v>
@@ -1158,30 +1233,30 @@
         <v>21</v>
       </c>
       <c r="I15" s="3">
-        <v>147075</v>
+        <v>8547166</v>
       </c>
       <c r="J15" s="3">
-        <v>147075</v>
+        <v>8547166</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F16" s="4">
-        <v>45959</v>
+        <v>45973</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>20</v>
@@ -1190,30 +1265,30 @@
         <v>21</v>
       </c>
       <c r="I16" s="3">
-        <v>108225</v>
+        <v>1097956</v>
       </c>
       <c r="J16" s="3">
-        <v>108225</v>
+        <v>1097956</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F17" s="4">
-        <v>45961</v>
+        <v>45973</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>20</v>
@@ -1222,10 +1297,10 @@
         <v>21</v>
       </c>
       <c r="I17" s="3">
-        <v>108225</v>
+        <v>104895</v>
       </c>
       <c r="J17" s="3">
-        <v>108225</v>
+        <v>104895</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -1233,7 +1308,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>17</v>
@@ -1245,7 +1320,7 @@
         <v>19</v>
       </c>
       <c r="F18" s="4">
-        <v>45959</v>
+        <v>45964</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>20</v>
@@ -1254,18 +1329,18 @@
         <v>21</v>
       </c>
       <c r="I18" s="3">
-        <v>527250</v>
+        <v>2156776</v>
       </c>
       <c r="J18" s="3">
-        <v>527250</v>
+        <v>2156776</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>17</v>
@@ -1274,10 +1349,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F19" s="4">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>20</v>
@@ -1286,18 +1361,18 @@
         <v>21</v>
       </c>
       <c r="I19" s="3">
-        <v>2354865</v>
+        <v>1800095</v>
       </c>
       <c r="J19" s="3">
-        <v>2354865</v>
+        <v>1800095</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>17</v>
@@ -1306,10 +1381,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F20" s="4">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>20</v>
@@ -1318,18 +1393,18 @@
         <v>21</v>
       </c>
       <c r="I20" s="3">
-        <v>234476</v>
+        <v>380512</v>
       </c>
       <c r="J20" s="3">
-        <v>234476</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>17</v>
@@ -1338,10 +1413,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F21" s="4">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>20</v>
@@ -1350,18 +1425,18 @@
         <v>21</v>
       </c>
       <c r="I21" s="3">
-        <v>19032948</v>
+        <v>197435</v>
       </c>
       <c r="J21" s="3">
-        <v>19032948</v>
+        <v>195727</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>17</v>
@@ -1370,10 +1445,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F22" s="4">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>20</v>
@@ -1382,18 +1457,18 @@
         <v>21</v>
       </c>
       <c r="I22" s="3">
-        <v>201465</v>
+        <v>380512</v>
       </c>
       <c r="J22" s="3">
-        <v>201465</v>
+        <v>33504</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>17</v>
@@ -1402,10 +1477,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F23" s="4">
-        <v>45961</v>
+        <v>45966</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>20</v>
@@ -1414,30 +1489,30 @@
         <v>21</v>
       </c>
       <c r="I23" s="3">
-        <v>727605</v>
+        <v>197435</v>
       </c>
       <c r="J23" s="3">
-        <v>727605</v>
+        <v>37740</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F24" s="4">
-        <v>45959</v>
+        <v>45975</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>20</v>
@@ -1446,30 +1521,30 @@
         <v>21</v>
       </c>
       <c r="I24" s="3">
-        <v>269730</v>
+        <v>47452</v>
       </c>
       <c r="J24" s="3">
-        <v>269730</v>
+        <v>47452</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F25" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>20</v>
@@ -1478,30 +1553,30 @@
         <v>21</v>
       </c>
       <c r="I25" s="3">
-        <v>201465</v>
+        <v>789210</v>
       </c>
       <c r="J25" s="3">
-        <v>201465</v>
+        <v>789210</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F26" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>20</v>
@@ -1510,30 +1585,30 @@
         <v>21</v>
       </c>
       <c r="I26" s="3">
-        <v>365745</v>
+        <v>108225</v>
       </c>
       <c r="J26" s="3">
-        <v>365745</v>
+        <v>108225</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F27" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>20</v>
@@ -1542,30 +1617,30 @@
         <v>21</v>
       </c>
       <c r="I27" s="3">
-        <v>852480</v>
+        <v>201465</v>
       </c>
       <c r="J27" s="3">
-        <v>852480</v>
+        <v>201465</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F28" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>20</v>
@@ -1574,30 +1649,30 @@
         <v>21</v>
       </c>
       <c r="I28" s="3">
-        <v>799200</v>
+        <v>1864800</v>
       </c>
       <c r="J28" s="3">
-        <v>799200</v>
+        <v>1864800</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F29" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>20</v>
@@ -1614,22 +1689,22 @@
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F30" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>20</v>
@@ -1638,30 +1713,30 @@
         <v>21</v>
       </c>
       <c r="I30" s="3">
-        <v>236985</v>
+        <v>979075</v>
       </c>
       <c r="J30" s="3">
-        <v>236985</v>
+        <v>979075</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F31" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>20</v>
@@ -1670,30 +1745,30 @@
         <v>21</v>
       </c>
       <c r="I31" s="3">
-        <v>2077920</v>
+        <v>266400</v>
       </c>
       <c r="J31" s="3">
-        <v>2077920</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="F32" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>20</v>
@@ -1702,30 +1777,30 @@
         <v>21</v>
       </c>
       <c r="I32" s="3">
-        <v>166500</v>
+        <v>1065600</v>
       </c>
       <c r="J32" s="3">
-        <v>166500</v>
+        <v>1065600</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F33" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>20</v>
@@ -1734,30 +1809,30 @@
         <v>21</v>
       </c>
       <c r="I33" s="3">
-        <v>532800</v>
+        <v>31635</v>
       </c>
       <c r="J33" s="3">
-        <v>532800</v>
+        <v>31635</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F34" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>20</v>
@@ -1766,30 +1841,30 @@
         <v>21</v>
       </c>
       <c r="I34" s="3">
-        <v>4270725</v>
+        <v>47452</v>
       </c>
       <c r="J34" s="3">
-        <v>4270725</v>
+        <v>47452</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F35" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>20</v>
@@ -1798,30 +1873,30 @@
         <v>21</v>
       </c>
       <c r="I35" s="3">
-        <v>304806</v>
+        <v>926295</v>
       </c>
       <c r="J35" s="3">
-        <v>304806</v>
+        <v>926295</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F36" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>20</v>
@@ -1830,30 +1905,30 @@
         <v>21</v>
       </c>
       <c r="I36" s="3">
-        <v>53280</v>
+        <v>1864800</v>
       </c>
       <c r="J36" s="3">
-        <v>53280</v>
+        <v>1864800</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F37" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>20</v>
@@ -1862,30 +1937,30 @@
         <v>21</v>
       </c>
       <c r="I37" s="3">
-        <v>1332000</v>
+        <v>555000</v>
       </c>
       <c r="J37" s="3">
-        <v>1332000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F38" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>20</v>
@@ -1894,30 +1969,30 @@
         <v>21</v>
       </c>
       <c r="I38" s="3">
-        <v>639360</v>
+        <v>532800</v>
       </c>
       <c r="J38" s="3">
-        <v>639360</v>
+        <v>532800</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F39" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>20</v>
@@ -1926,30 +2001,30 @@
         <v>21</v>
       </c>
       <c r="I39" s="3">
-        <v>244755</v>
+        <v>1010100</v>
       </c>
       <c r="J39" s="3">
-        <v>244755</v>
+        <v>1010100</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F40" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>20</v>
@@ -1958,30 +2033,30 @@
         <v>21</v>
       </c>
       <c r="I40" s="3">
-        <v>5328000</v>
+        <v>138750</v>
       </c>
       <c r="J40" s="3">
-        <v>5328000</v>
+        <v>138750</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F41" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>20</v>
@@ -1990,30 +2065,30 @@
         <v>21</v>
       </c>
       <c r="I41" s="3">
-        <v>69375</v>
+        <v>111055</v>
       </c>
       <c r="J41" s="3">
-        <v>69375</v>
+        <v>111055</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F42" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>20</v>
@@ -2022,30 +2097,30 @@
         <v>21</v>
       </c>
       <c r="I42" s="3">
-        <v>36075</v>
+        <v>144300</v>
       </c>
       <c r="J42" s="3">
-        <v>36075</v>
+        <v>144300</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F43" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>20</v>
@@ -2054,30 +2129,30 @@
         <v>21</v>
       </c>
       <c r="I43" s="3">
-        <v>7104000</v>
+        <v>2024640</v>
       </c>
       <c r="J43" s="3">
-        <v>7104000</v>
+        <v>2024640</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>48</v>
+        <v>77</v>
       </c>
       <c r="F44" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>20</v>
@@ -2086,30 +2161,30 @@
         <v>21</v>
       </c>
       <c r="I44" s="3">
-        <v>2664000</v>
+        <v>308726</v>
       </c>
       <c r="J44" s="3">
-        <v>2664000</v>
+        <v>308726</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F45" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>20</v>
@@ -2118,30 +2193,30 @@
         <v>21</v>
       </c>
       <c r="I45" s="3">
-        <v>271395</v>
+        <v>31635</v>
       </c>
       <c r="J45" s="3">
-        <v>271395</v>
+        <v>31635</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F46" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>20</v>
@@ -2150,30 +2225,30 @@
         <v>21</v>
       </c>
       <c r="I46" s="3">
-        <v>1132200</v>
+        <v>109890</v>
       </c>
       <c r="J46" s="3">
-        <v>1132200</v>
+        <v>109890</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F47" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>20</v>
@@ -2182,30 +2257,30 @@
         <v>21</v>
       </c>
       <c r="I47" s="3">
-        <v>245310</v>
+        <v>430015</v>
       </c>
       <c r="J47" s="3">
-        <v>245310</v>
+        <v>430015</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F48" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>20</v>
@@ -2214,30 +2289,30 @@
         <v>21</v>
       </c>
       <c r="I48" s="3">
-        <v>213120</v>
+        <v>138750</v>
       </c>
       <c r="J48" s="3">
-        <v>213120</v>
+        <v>138750</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F49" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>20</v>
@@ -2246,30 +2321,30 @@
         <v>21</v>
       </c>
       <c r="I49" s="3">
-        <v>799200</v>
+        <v>639360</v>
       </c>
       <c r="J49" s="3">
-        <v>799200</v>
+        <v>639360</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F50" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>20</v>
@@ -2278,30 +2353,30 @@
         <v>21</v>
       </c>
       <c r="I50" s="3">
-        <v>489510</v>
+        <v>2150625</v>
       </c>
       <c r="J50" s="3">
-        <v>489510</v>
+        <v>2150625</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="F51" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>20</v>
@@ -2310,30 +2385,30 @@
         <v>21</v>
       </c>
       <c r="I51" s="3">
-        <v>4162500</v>
+        <v>222027</v>
       </c>
       <c r="J51" s="3">
-        <v>4162500</v>
+        <v>222027</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F52" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>20</v>
@@ -2342,30 +2417,30 @@
         <v>21</v>
       </c>
       <c r="I52" s="3">
-        <v>353414</v>
+        <v>394605</v>
       </c>
       <c r="J52" s="3">
-        <v>353414</v>
+        <v>394605</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="F53" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>20</v>
@@ -2374,30 +2449,30 @@
         <v>21</v>
       </c>
       <c r="I53" s="3">
-        <v>132018</v>
+        <v>104895</v>
       </c>
       <c r="J53" s="3">
-        <v>132018</v>
+        <v>104895</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="F54" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>20</v>
@@ -2406,30 +2481,30 @@
         <v>21</v>
       </c>
       <c r="I54" s="3">
-        <v>1818653</v>
+        <v>224775</v>
       </c>
       <c r="J54" s="3">
-        <v>1818653</v>
+        <v>224775</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="F55" s="4">
-        <v>45952</v>
+        <v>45975</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>20</v>
@@ -2438,30 +2513,30 @@
         <v>21</v>
       </c>
       <c r="I55" s="3">
-        <v>989942</v>
+        <v>1887000</v>
       </c>
       <c r="J55" s="3">
-        <v>989942</v>
+        <v>1887000</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F56" s="4">
-        <v>45954</v>
+        <v>45966</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>20</v>
@@ -2470,30 +2545,30 @@
         <v>21</v>
       </c>
       <c r="I56" s="3">
-        <v>13059150</v>
+        <v>1818653</v>
       </c>
       <c r="J56" s="3">
-        <v>13059150</v>
+        <v>1818653</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="F57" s="4">
-        <v>45954</v>
+        <v>45975</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>20</v>
@@ -2502,62 +2577,62 @@
         <v>21</v>
       </c>
       <c r="I57" s="3">
-        <v>2207790</v>
+        <v>2316718</v>
       </c>
       <c r="J57" s="3">
-        <v>2207790</v>
+        <v>2316718</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F58" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="I58" s="3">
-        <v>-262311</v>
+        <v>3731814</v>
       </c>
       <c r="J58" s="3">
-        <v>-262311</v>
+        <v>3731814</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B59" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F59" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>20</v>
@@ -2566,30 +2641,30 @@
         <v>21</v>
       </c>
       <c r="I59" s="3">
-        <v>197435</v>
+        <v>1751802</v>
       </c>
       <c r="J59" s="3">
-        <v>197435</v>
+        <v>1751802</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B60" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="F60" s="4">
-        <v>45959</v>
+        <v>45975</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>20</v>
@@ -2598,30 +2673,30 @@
         <v>21</v>
       </c>
       <c r="I60" s="3">
-        <v>592307</v>
+        <v>1278720</v>
       </c>
       <c r="J60" s="3">
-        <v>592307</v>
+        <v>1278720</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F61" s="4">
-        <v>45959</v>
+        <v>45975</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>20</v>
@@ -2630,30 +2705,30 @@
         <v>21</v>
       </c>
       <c r="I61" s="3">
-        <v>4539609</v>
+        <v>10516015</v>
       </c>
       <c r="J61" s="3">
-        <v>4539609</v>
+        <v>10516015</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F62" s="4">
-        <v>45959</v>
+        <v>45975</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>20</v>
@@ -2662,30 +2737,30 @@
         <v>21</v>
       </c>
       <c r="I62" s="3">
-        <v>1078388</v>
+        <v>922211</v>
       </c>
       <c r="J62" s="3">
-        <v>1078388</v>
+        <v>922211</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="F63" s="4">
-        <v>45959</v>
+        <v>45971</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>20</v>
@@ -2694,30 +2769,30 @@
         <v>21</v>
       </c>
       <c r="I63" s="3">
-        <v>380512</v>
+        <v>11982608</v>
       </c>
       <c r="J63" s="3">
-        <v>380512</v>
+        <v>11982608</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F64" s="4">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>20</v>
@@ -2726,30 +2801,30 @@
         <v>21</v>
       </c>
       <c r="I64" s="3">
-        <v>197435</v>
+        <v>3007975</v>
       </c>
       <c r="J64" s="3">
-        <v>197435</v>
+        <v>3007975</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F65" s="4">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>20</v>
@@ -2758,30 +2833,30 @@
         <v>21</v>
       </c>
       <c r="I65" s="3">
-        <v>4539581</v>
+        <v>1081237</v>
       </c>
       <c r="J65" s="3">
-        <v>4539581</v>
+        <v>1081237</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F66" s="4">
-        <v>45961</v>
+        <v>45971</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>20</v>
@@ -2790,94 +2865,94 @@
         <v>21</v>
       </c>
       <c r="I66" s="3">
-        <v>2521803</v>
+        <v>2697566</v>
       </c>
       <c r="J66" s="3">
-        <v>2521803</v>
+        <v>2697566</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F67" s="4">
-        <v>45961</v>
+        <v>45972</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="I67" s="3">
-        <v>197435</v>
+        <v>-37773</v>
       </c>
       <c r="J67" s="3">
-        <v>197435</v>
+        <v>-37773</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F68" s="4">
-        <v>45961</v>
+        <v>45972</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>21</v>
+        <v>117</v>
       </c>
       <c r="I68" s="3">
-        <v>1488057</v>
+        <v>-126318</v>
       </c>
       <c r="J68" s="3">
-        <v>1488057</v>
+        <v>-126318</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>114</v>
+        <v>17</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="F69" s="4">
-        <v>45961</v>
+        <v>45975</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>20</v>
@@ -2886,30 +2961,30 @@
         <v>21</v>
       </c>
       <c r="I69" s="3">
-        <v>2062573</v>
+        <v>1056153</v>
       </c>
       <c r="J69" s="3">
-        <v>204399</v>
+        <v>1056153</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F70" s="4">
-        <v>45961</v>
+        <v>45974</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>20</v>
@@ -2918,62 +2993,62 @@
         <v>21</v>
       </c>
       <c r="I70" s="3">
-        <v>502293</v>
+        <v>2095198</v>
       </c>
       <c r="J70" s="3">
-        <v>49776</v>
+        <v>2095198</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F71" s="4">
-        <v>45961</v>
+        <v>45974</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="I71" s="3">
-        <v>-11730200</v>
+        <v>9926119</v>
       </c>
       <c r="J71" s="3">
-        <v>-2622783</v>
+        <v>9926119</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="F72" s="4">
-        <v>45961</v>
+        <v>45974</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>20</v>
@@ -2982,30 +3057,30 @@
         <v>21</v>
       </c>
       <c r="I72" s="3">
-        <v>1298700</v>
+        <v>11788072</v>
       </c>
       <c r="J72" s="3">
-        <v>1298700</v>
+        <v>5898744</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F73" s="4">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>20</v>
@@ -3014,30 +3089,30 @@
         <v>21</v>
       </c>
       <c r="I73" s="3">
-        <v>270751</v>
+        <v>380512</v>
       </c>
       <c r="J73" s="3">
-        <v>270751</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F74" s="4">
-        <v>45960</v>
+        <v>45975</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>20</v>
@@ -3046,30 +3121,30 @@
         <v>21</v>
       </c>
       <c r="I74" s="3">
-        <v>589001</v>
+        <v>402050</v>
       </c>
       <c r="J74" s="3">
-        <v>589001</v>
+        <v>402050</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F75" s="4">
-        <v>45960</v>
+        <v>45975</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>20</v>
@@ -3078,30 +3153,30 @@
         <v>21</v>
       </c>
       <c r="I75" s="3">
-        <v>180500</v>
+        <v>197435</v>
       </c>
       <c r="J75" s="3">
-        <v>180500</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="76" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>127</v>
+        <v>54</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F76" s="4">
-        <v>45960</v>
+        <v>45975</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>20</v>
@@ -3110,30 +3185,30 @@
         <v>21</v>
       </c>
       <c r="I76" s="3">
-        <v>275499</v>
+        <v>197435</v>
       </c>
       <c r="J76" s="3">
-        <v>275499</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="77" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>136</v>
       </c>
       <c r="F77" s="4">
-        <v>45960</v>
+        <v>45975</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>20</v>
@@ -3142,30 +3217,30 @@
         <v>21</v>
       </c>
       <c r="I77" s="3">
-        <v>350535</v>
+        <v>197435</v>
       </c>
       <c r="J77" s="3">
-        <v>350535</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>136</v>
       </c>
       <c r="F78" s="4">
-        <v>45960</v>
+        <v>45975</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>20</v>
@@ -3174,10 +3249,490 @@
         <v>21</v>
       </c>
       <c r="I78" s="3">
-        <v>1734264</v>
+        <v>2095198</v>
       </c>
       <c r="J78" s="3">
-        <v>1734264</v>
+        <v>2095198</v>
+      </c>
+    </row>
+    <row r="79" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A79" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F79" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="3">
+        <v>941626</v>
+      </c>
+      <c r="J79" s="3">
+        <v>941626</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A80" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F80" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="3">
+        <v>1078388</v>
+      </c>
+      <c r="J80" s="3">
+        <v>1078388</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A81" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F81" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I81" s="3">
+        <v>402050</v>
+      </c>
+      <c r="J81" s="3">
+        <v>402050</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A82" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F82" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I82" s="3">
+        <v>197435</v>
+      </c>
+      <c r="J82" s="3">
+        <v>197435</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A83" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F83" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I83" s="3">
+        <v>197435</v>
+      </c>
+      <c r="J83" s="3">
+        <v>197435</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A84" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F84" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I84" s="3">
+        <v>380512</v>
+      </c>
+      <c r="J84" s="3">
+        <v>380512</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A85" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F85" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I85" s="3">
+        <v>175000</v>
+      </c>
+      <c r="J85" s="3">
+        <v>175000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A86" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="F86" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I86" s="3">
+        <v>144550</v>
+      </c>
+      <c r="J86" s="3">
+        <v>144550</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A87" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F87" s="4">
+        <v>45974</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I87" s="3">
+        <v>133200</v>
+      </c>
+      <c r="J87" s="3">
+        <v>133200</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A88" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="F88" s="4">
+        <v>45975</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I88" s="3">
+        <v>355200</v>
+      </c>
+      <c r="J88" s="3">
+        <v>355200</v>
+      </c>
+    </row>
+    <row r="89" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A89" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F89" s="4">
+        <v>45974</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I89" s="3">
+        <v>1348650</v>
+      </c>
+      <c r="J89" s="3">
+        <v>1348650</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A90" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F90" s="4">
+        <v>45974</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I90" s="3">
+        <v>333000</v>
+      </c>
+      <c r="J90" s="3">
+        <v>333000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A91" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F91" s="4">
+        <v>45974</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I91" s="3">
+        <v>700683</v>
+      </c>
+      <c r="J91" s="3">
+        <v>700683</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A92" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F92" s="4">
+        <v>45974</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I92" s="3">
+        <v>368181</v>
+      </c>
+      <c r="J92" s="3">
+        <v>368181</v>
+      </c>
+    </row>
+    <row r="93" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F93" s="4">
+        <v>45974</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I93" s="3">
+        <v>183072</v>
+      </c>
+      <c r="J93" s="3">
+        <v>183072</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/transfer.xlsx
+++ b/uploads/transfer.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251114\Eksport\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29613FC0-3F95-4423-A7E3-B2FAF9233AEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Intransit Transfer Outstanding" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="144">
   <si>
     <t>nomor_request</t>
   </si>
@@ -66,99 +67,213 @@
     <t>ex: angka</t>
   </si>
   <si>
-    <t>2826ACH25000015</t>
-  </si>
-  <si>
-    <t>25ASB24015854</t>
+    <t>0826ACH25000039</t>
+  </si>
+  <si>
+    <t>08ASB25018184</t>
+  </si>
+  <si>
+    <t>BOGOR</t>
+  </si>
+  <si>
+    <t>BEKASI</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Intransit</t>
+  </si>
+  <si>
+    <t>OUTSTANDING</t>
+  </si>
+  <si>
+    <t>08ASB25018185</t>
+  </si>
+  <si>
+    <t>08ASB25018186</t>
+  </si>
+  <si>
+    <t>08ASB25018187</t>
+  </si>
+  <si>
+    <t>08ASB25018188</t>
+  </si>
+  <si>
+    <t>08ASB25018191</t>
+  </si>
+  <si>
+    <t>08ASB25018192</t>
+  </si>
+  <si>
+    <t>08ASB25018193</t>
+  </si>
+  <si>
+    <t>08ASB25018195</t>
+  </si>
+  <si>
+    <t>08ASB25018250</t>
+  </si>
+  <si>
+    <t>08ASB25018275</t>
+  </si>
+  <si>
+    <t>08ASB25018276</t>
+  </si>
+  <si>
+    <t>08ASB25018277</t>
+  </si>
+  <si>
+    <t>08ASB25018286</t>
+  </si>
+  <si>
+    <t>08ASB25018287</t>
+  </si>
+  <si>
+    <t>08ASB25018301</t>
+  </si>
+  <si>
+    <t>08ASB25018373</t>
+  </si>
+  <si>
+    <t>08ASB25018387</t>
+  </si>
+  <si>
+    <t>08ASB25018388</t>
+  </si>
+  <si>
+    <t>08ASB25018403</t>
+  </si>
+  <si>
+    <t>08ASB25018404</t>
+  </si>
+  <si>
+    <t>08ASB25018405</t>
+  </si>
+  <si>
+    <t>08ASB25018406</t>
+  </si>
+  <si>
+    <t>08ASB25018407</t>
+  </si>
+  <si>
+    <t>08ASB25018445</t>
+  </si>
+  <si>
+    <t>08ASB25018467</t>
+  </si>
+  <si>
+    <t>08ASB25018471</t>
+  </si>
+  <si>
+    <t>08ASB25018472</t>
+  </si>
+  <si>
+    <t>08ASB25018515</t>
+  </si>
+  <si>
+    <t>08ASB25018521</t>
+  </si>
+  <si>
+    <t>08ASB25018522</t>
+  </si>
+  <si>
+    <t>08ASB25018524</t>
+  </si>
+  <si>
+    <t>08ASB25018586</t>
+  </si>
+  <si>
+    <t>08ASB25018596</t>
+  </si>
+  <si>
+    <t>08ASB25018597</t>
+  </si>
+  <si>
+    <t>08ASB25018622</t>
+  </si>
+  <si>
+    <t>08ASB25018623</t>
+  </si>
+  <si>
+    <t>08ASB25018628</t>
+  </si>
+  <si>
+    <t>08ASB25018629</t>
+  </si>
+  <si>
+    <t>08ASB25018630</t>
+  </si>
+  <si>
+    <t>08ASB25018631</t>
+  </si>
+  <si>
+    <t>08ASB25018632</t>
+  </si>
+  <si>
+    <t>08ASB25018633</t>
+  </si>
+  <si>
+    <t>08ASB25018641</t>
+  </si>
+  <si>
+    <t>08ASB25018694</t>
+  </si>
+  <si>
+    <t>08ASB25018695</t>
+  </si>
+  <si>
+    <t>08ASB25018696</t>
+  </si>
+  <si>
+    <t>08ASB25018697</t>
+  </si>
+  <si>
+    <t>08ASB25018698</t>
+  </si>
+  <si>
+    <t>08ASB25018699</t>
+  </si>
+  <si>
+    <t>0826BCH25000014</t>
+  </si>
+  <si>
+    <t>08BSB25001003</t>
+  </si>
+  <si>
+    <t>2526ACH25000114</t>
+  </si>
+  <si>
+    <t>25ASB25019605</t>
+  </si>
+  <si>
+    <t>TANGERANG</t>
+  </si>
+  <si>
+    <t>TF MITRA KALIDERES DI BEKASI</t>
+  </si>
+  <si>
+    <t>25ASB25019606</t>
+  </si>
+  <si>
+    <t>25ASB25019647</t>
+  </si>
+  <si>
+    <t>25ASB25019664</t>
+  </si>
+  <si>
+    <t>25ASB25019764</t>
+  </si>
+  <si>
+    <t>2826ACH25000016</t>
+  </si>
+  <si>
+    <t>26ASB25020250</t>
   </si>
   <si>
     <t>PUSAT (PIUTANG)</t>
   </si>
   <si>
-    <t>BEKASI</t>
-  </si>
-  <si>
-    <t>POT RETUR TRANSMART PEMBAYARAN 30.05.25</t>
-  </si>
-  <si>
-    <t>Intransit</t>
-  </si>
-  <si>
-    <t>OUTSTANDING</t>
-  </si>
-  <si>
-    <t>2526ACH25000108</t>
-  </si>
-  <si>
-    <t>25ASB25017920</t>
-  </si>
-  <si>
-    <t>TANGERANG</t>
-  </si>
-  <si>
-    <t>TF MITRA KELUARGA GADING SERPONG</t>
-  </si>
-  <si>
-    <t>2526ACH25000107</t>
-  </si>
-  <si>
-    <t>25ASB25017934</t>
-  </si>
-  <si>
-    <t>TF RSU MITRA KALIDERES</t>
-  </si>
-  <si>
-    <t>25ASB25017970</t>
-  </si>
-  <si>
-    <t>25ASB25017971</t>
-  </si>
-  <si>
-    <t>25ASB25017994</t>
-  </si>
-  <si>
-    <t>25ASB25017995</t>
-  </si>
-  <si>
-    <t>25ASB25017996</t>
-  </si>
-  <si>
-    <t>25ASB25018077</t>
-  </si>
-  <si>
-    <t>25ASB25018110</t>
-  </si>
-  <si>
-    <t>25ASB25018190</t>
-  </si>
-  <si>
-    <t>25ASB25018235</t>
-  </si>
-  <si>
-    <t>25ASB25018247</t>
-  </si>
-  <si>
-    <t>2526BCH25000039</t>
-  </si>
-  <si>
-    <t>25BSB25001513</t>
-  </si>
-  <si>
-    <t>TF MITRA GADING SERPONG</t>
-  </si>
-  <si>
-    <t>26ASB24021414</t>
-  </si>
-  <si>
-    <t>26ASB24022295</t>
-  </si>
-  <si>
-    <t>2826ACH25000016</t>
-  </si>
-  <si>
-    <t>26ASB25020250</t>
-  </si>
-  <si>
     <t>POT RETUR WATSON BKS KPO 16.10.2025</t>
   </si>
   <si>
@@ -174,235 +289,61 @@
     <t>POT RETUR WATSON BKS KPO 27.10.2025</t>
   </si>
   <si>
+    <t>2826ACH25000018</t>
+  </si>
+  <si>
+    <t>26ASB25026401</t>
+  </si>
+  <si>
+    <t>POT RETUR TIPTOP BKS GIRO 717952</t>
+  </si>
+  <si>
     <t>27ASB25014375</t>
   </si>
   <si>
-    <t>2726ACH25000076</t>
-  </si>
-  <si>
-    <t>27ASB25019936</t>
+    <t>2808ACH25000009</t>
+  </si>
+  <si>
+    <t>07ASB25031653</t>
+  </si>
+  <si>
+    <t>POT RETUR TIPTOP BCA 05.11.2025</t>
+  </si>
+  <si>
+    <t>0727ACH25000111</t>
+  </si>
+  <si>
+    <t>07ASB25037663</t>
+  </si>
+  <si>
+    <t>JAKARTA PUSAT</t>
   </si>
   <si>
     <t>JAKARTA SELATAN</t>
   </si>
   <si>
-    <t>TUKAR FAKTUR DI BKS</t>
-  </si>
-  <si>
-    <t>27ASB25019937</t>
-  </si>
-  <si>
-    <t>27ASB25019949</t>
-  </si>
-  <si>
-    <t>27ASB25019950</t>
-  </si>
-  <si>
-    <t>27ASB25019951</t>
-  </si>
-  <si>
-    <t>27ASB25019952</t>
-  </si>
-  <si>
-    <t>27ASB25019953</t>
-  </si>
-  <si>
-    <t>27ASB25019954</t>
-  </si>
-  <si>
-    <t>27ASB25019955</t>
-  </si>
-  <si>
-    <t>27ASB25020020</t>
-  </si>
-  <si>
-    <t>27ASB25020128</t>
-  </si>
-  <si>
-    <t>27ASB25020129</t>
-  </si>
-  <si>
-    <t>27ASB25020216</t>
-  </si>
-  <si>
-    <t>27ASB25020217</t>
-  </si>
-  <si>
-    <t>27ASB25020218</t>
-  </si>
-  <si>
-    <t>27ASB25020219</t>
-  </si>
-  <si>
-    <t>27ASB25020220</t>
-  </si>
-  <si>
-    <t>27ASB25020221</t>
-  </si>
-  <si>
-    <t>27ASB25020222</t>
-  </si>
-  <si>
-    <t>27ASB25020253</t>
-  </si>
-  <si>
-    <t>2726ACH25000075</t>
-  </si>
-  <si>
-    <t>27ASB25020299</t>
-  </si>
-  <si>
-    <t>NAGA SWALAYAN</t>
-  </si>
-  <si>
-    <t>27ASB25020314</t>
-  </si>
-  <si>
-    <t>27ASB25020419</t>
-  </si>
-  <si>
-    <t>27ASB25020428</t>
-  </si>
-  <si>
-    <t>27ASB25020451</t>
-  </si>
-  <si>
-    <t>27ASB25020452</t>
-  </si>
-  <si>
-    <t>27ASB25020453</t>
-  </si>
-  <si>
-    <t>27ASB25020454</t>
-  </si>
-  <si>
-    <t>27ASB25020455</t>
-  </si>
-  <si>
-    <t>2726BCH25000023</t>
-  </si>
-  <si>
-    <t>27BSB25000643</t>
-  </si>
-  <si>
-    <t>27BSB25000650</t>
-  </si>
-  <si>
-    <t>1801BCH25000001</t>
-  </si>
-  <si>
-    <t>18BSB25000214</t>
-  </si>
-  <si>
-    <t>PUSAT 79</t>
-  </si>
-  <si>
-    <t>CIREBON</t>
-  </si>
-  <si>
-    <t>KP.CIREBON</t>
-  </si>
-  <si>
-    <t>2807ACH25000091</t>
-  </si>
-  <si>
-    <t>07ASB24028161</t>
-  </si>
-  <si>
-    <t>JAKARTA PUSAT</t>
-  </si>
-  <si>
-    <t>PENGEMBALIAN PIUTANG JAKPUS</t>
-  </si>
-  <si>
-    <t>2707ACH25000073</t>
-  </si>
-  <si>
-    <t>07ASB25034549</t>
-  </si>
-  <si>
-    <t>BRAWIJAYA SDH TUKAR</t>
-  </si>
-  <si>
-    <t>07ASB25034824</t>
-  </si>
-  <si>
-    <t>07ASB25034950</t>
-  </si>
-  <si>
-    <t>07ASB25034968</t>
-  </si>
-  <si>
-    <t>07ASB25035316</t>
-  </si>
-  <si>
-    <t>2807ACH25000092</t>
-  </si>
-  <si>
-    <t>25ASB25014626</t>
-  </si>
-  <si>
-    <t>PEMBAYARAN DI JAKPUS KPO 12.11.2025</t>
-  </si>
-  <si>
-    <t>2507ACH25000042</t>
-  </si>
-  <si>
-    <t>25ASB25017826</t>
-  </si>
-  <si>
-    <t>TF DI JAKPUS</t>
-  </si>
-  <si>
-    <t>25ASB25017911</t>
-  </si>
-  <si>
-    <t>25ASB25018023</t>
-  </si>
-  <si>
-    <t>25ASB25018254</t>
-  </si>
-  <si>
-    <t>2507ACH25000043</t>
-  </si>
-  <si>
-    <t>25ASG25000380</t>
-  </si>
-  <si>
-    <t>CN ERA CARING</t>
-  </si>
-  <si>
-    <t>DEPOSIT</t>
-  </si>
-  <si>
-    <t>25ASG25000417</t>
-  </si>
-  <si>
-    <t>27ASB25015642</t>
-  </si>
-  <si>
-    <t>2707ACH25000071</t>
-  </si>
-  <si>
-    <t>27ASB25017192</t>
-  </si>
-  <si>
-    <t>HOKKY BERSAMA</t>
-  </si>
-  <si>
-    <t>2707ACH25000072</t>
-  </si>
-  <si>
-    <t>27ASB25020038</t>
-  </si>
-  <si>
-    <t>TUKAR FAKTUR DI JAKPUS</t>
-  </si>
-  <si>
-    <t>0700ACH25000059</t>
-  </si>
-  <si>
-    <t>07ASB25035953</t>
+    <t>TF DI SELATAN</t>
+  </si>
+  <si>
+    <t>07ASB25037742</t>
+  </si>
+  <si>
+    <t>07ASB25038078</t>
+  </si>
+  <si>
+    <t>07ASB25038091</t>
+  </si>
+  <si>
+    <t>0827ACH25000028</t>
+  </si>
+  <si>
+    <t>08ASB25017561</t>
+  </si>
+  <si>
+    <t>0700ACH25000063</t>
+  </si>
+  <si>
+    <t>07ASB25037908</t>
   </si>
   <si>
     <t>KANTOR PUSAT</t>
@@ -411,109 +352,112 @@
     <t>POT RAFRAKSI</t>
   </si>
   <si>
-    <t>1328ACH25000007</t>
-  </si>
-  <si>
-    <t>13ASB25016823</t>
-  </si>
-  <si>
-    <t>YOGYAKARTA</t>
-  </si>
-  <si>
-    <t>PENGALIHAN PIUTANG WATSON GALERIA</t>
-  </si>
-  <si>
-    <t>2728ACH25000050</t>
-  </si>
-  <si>
-    <t>27ASB25019812</t>
-  </si>
-  <si>
-    <t>TIPTOP, GRANDLUCKY, WATSONS</t>
-  </si>
-  <si>
-    <t>27ASB25020081</t>
-  </si>
-  <si>
-    <t>27ASB25020087</t>
-  </si>
-  <si>
-    <t>27ASB25020089</t>
-  </si>
-  <si>
-    <t>27ASB25020092</t>
-  </si>
-  <si>
-    <t>27ASB25020095</t>
-  </si>
-  <si>
-    <t>27ASB25020143</t>
-  </si>
-  <si>
-    <t>27ASB25020179</t>
-  </si>
-  <si>
-    <t>27ASB25020284</t>
-  </si>
-  <si>
-    <t>27ASB25020285</t>
-  </si>
-  <si>
-    <t>27ASB25020316</t>
-  </si>
-  <si>
-    <t>2725ACH25000054</t>
-  </si>
-  <si>
-    <t>25ASB25016769</t>
-  </si>
-  <si>
-    <t>25ASB25017546</t>
-  </si>
-  <si>
-    <t>2725ACH25000053</t>
-  </si>
-  <si>
-    <t>27ASB25020265</t>
+    <t>1600ACH25000007</t>
+  </si>
+  <si>
+    <t>16ASB25020042</t>
+  </si>
+  <si>
+    <t>DENPASAR</t>
+  </si>
+  <si>
+    <t>PENGALIHAN POT LISTING</t>
+  </si>
+  <si>
+    <t>16ASB25020402</t>
+  </si>
+  <si>
+    <t>0228ACH25000011</t>
+  </si>
+  <si>
+    <t>02ASB25020598</t>
+  </si>
+  <si>
+    <t>MEDAN</t>
+  </si>
+  <si>
+    <t>FAKTUR WATSONS MANHATTAN 29/11/25</t>
+  </si>
+  <si>
+    <t>0728ACH25000193</t>
+  </si>
+  <si>
+    <t>07ASB25038512</t>
+  </si>
+  <si>
+    <t>TF DI PUSAT</t>
+  </si>
+  <si>
+    <t>2328ACH25000028</t>
+  </si>
+  <si>
+    <t>23ASB25012778</t>
+  </si>
+  <si>
+    <t>SAMARINDA</t>
+  </si>
+  <si>
+    <t>2528ACH25000090</t>
+  </si>
+  <si>
+    <t>25ASB25019194</t>
+  </si>
+  <si>
+    <t>TUKER FAKTUR DI PUSAT</t>
+  </si>
+  <si>
+    <t>25ASB25019608</t>
+  </si>
+  <si>
+    <t>25ASB25019692</t>
+  </si>
+  <si>
+    <t>2728ACH25000052</t>
+  </si>
+  <si>
+    <t>27ASB25020868</t>
+  </si>
+  <si>
+    <t>HARI HARI, TIP TOP, DAN WATSONS</t>
+  </si>
+  <si>
+    <t>27ASB25020871</t>
+  </si>
+  <si>
+    <t>27ASB25021039</t>
+  </si>
+  <si>
+    <t>27ASB25021066</t>
+  </si>
+  <si>
+    <t>27ASB25021282</t>
+  </si>
+  <si>
+    <t>27ASB25021376</t>
+  </si>
+  <si>
+    <t>27ASB25021397</t>
+  </si>
+  <si>
+    <t>0725ACH25000017</t>
+  </si>
+  <si>
+    <t>07ASB25037346</t>
+  </si>
+  <si>
+    <t>2725ACH25000058</t>
+  </si>
+  <si>
+    <t>27ASB25021523</t>
   </si>
   <si>
     <t>TUKAR FAKTUR DI TGR</t>
-  </si>
-  <si>
-    <t>2725ACH25000055</t>
-  </si>
-  <si>
-    <t>27ASB25020635</t>
-  </si>
-  <si>
-    <t>1213ACH25000016</t>
-  </si>
-  <si>
-    <t>12ASB25021890</t>
-  </si>
-  <si>
-    <t>SOLO</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>12ASB25022059</t>
-  </si>
-  <si>
-    <t>12ASB25022087</t>
-  </si>
-  <si>
-    <t>12ASB25022431</t>
-  </si>
-  <si>
-    <t>12ASB25022464</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -779,11 +723,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J93"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -872,7 +816,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="4">
-        <v>45964</v>
+        <v>45993</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>20</v>
@@ -881,30 +825,30 @@
         <v>21</v>
       </c>
       <c r="I4" s="3">
-        <v>1078388</v>
+        <v>252525</v>
       </c>
       <c r="J4" s="3">
-        <v>37677</v>
+        <v>252525</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F5" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>20</v>
@@ -913,30 +857,30 @@
         <v>21</v>
       </c>
       <c r="I5" s="3">
-        <v>126540</v>
+        <v>426240</v>
       </c>
       <c r="J5" s="3">
-        <v>126540</v>
+        <v>426240</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F6" s="4">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>20</v>
@@ -945,30 +889,30 @@
         <v>21</v>
       </c>
       <c r="I6" s="3">
-        <v>685980</v>
+        <v>1007325</v>
       </c>
       <c r="J6" s="3">
-        <v>685980</v>
+        <v>1007325</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F7" s="4">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>20</v>
@@ -977,30 +921,30 @@
         <v>21</v>
       </c>
       <c r="I7" s="3">
-        <v>947995</v>
+        <v>3396600</v>
       </c>
       <c r="J7" s="3">
-        <v>947995</v>
+        <v>3396600</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F8" s="4">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>20</v>
@@ -1009,30 +953,30 @@
         <v>21</v>
       </c>
       <c r="I8" s="3">
-        <v>1804860</v>
+        <v>3468750</v>
       </c>
       <c r="J8" s="3">
-        <v>1804860</v>
+        <v>3468750</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F9" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -1041,30 +985,30 @@
         <v>21</v>
       </c>
       <c r="I9" s="3">
-        <v>1883670</v>
+        <v>627705</v>
       </c>
       <c r="J9" s="3">
-        <v>1883670</v>
+        <v>627705</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F10" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>20</v>
@@ -1073,30 +1017,30 @@
         <v>21</v>
       </c>
       <c r="I10" s="3">
-        <v>1638082</v>
+        <v>426240</v>
       </c>
       <c r="J10" s="3">
-        <v>1638082</v>
+        <v>426240</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F11" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>20</v>
@@ -1105,30 +1049,30 @@
         <v>21</v>
       </c>
       <c r="I11" s="3">
-        <v>1103284</v>
+        <v>321095</v>
       </c>
       <c r="J11" s="3">
-        <v>1103284</v>
+        <v>321095</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>20</v>
@@ -1137,30 +1081,30 @@
         <v>21</v>
       </c>
       <c r="I12" s="3">
-        <v>471599</v>
+        <v>1497112</v>
       </c>
       <c r="J12" s="3">
-        <v>471599</v>
+        <v>1497112</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F13" s="4">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>20</v>
@@ -1169,30 +1113,30 @@
         <v>21</v>
       </c>
       <c r="I13" s="3">
-        <v>143856</v>
+        <v>460372</v>
       </c>
       <c r="J13" s="3">
-        <v>143856</v>
+        <v>460372</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F14" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>20</v>
@@ -1201,30 +1145,30 @@
         <v>21</v>
       </c>
       <c r="I14" s="3">
-        <v>2664000</v>
+        <v>144044</v>
       </c>
       <c r="J14" s="3">
-        <v>2664000</v>
+        <v>144044</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F15" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>20</v>
@@ -1233,30 +1177,30 @@
         <v>21</v>
       </c>
       <c r="I15" s="3">
-        <v>8547166</v>
+        <v>36075</v>
       </c>
       <c r="J15" s="3">
-        <v>8547166</v>
+        <v>36075</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F16" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>20</v>
@@ -1265,30 +1209,30 @@
         <v>21</v>
       </c>
       <c r="I16" s="3">
-        <v>1097956</v>
+        <v>201465</v>
       </c>
       <c r="J16" s="3">
-        <v>1097956</v>
+        <v>201465</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F17" s="4">
-        <v>45973</v>
+        <v>45993</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>20</v>
@@ -1297,10 +1241,10 @@
         <v>21</v>
       </c>
       <c r="I17" s="3">
-        <v>104895</v>
+        <v>902385</v>
       </c>
       <c r="J17" s="3">
-        <v>104895</v>
+        <v>902385</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -1308,7 +1252,7 @@
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>17</v>
@@ -1320,7 +1264,7 @@
         <v>19</v>
       </c>
       <c r="F18" s="4">
-        <v>45964</v>
+        <v>45993</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>20</v>
@@ -1329,10 +1273,10 @@
         <v>21</v>
       </c>
       <c r="I18" s="3">
-        <v>2156776</v>
+        <v>166500</v>
       </c>
       <c r="J18" s="3">
-        <v>2156776</v>
+        <v>166500</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -1340,7 +1284,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>17</v>
@@ -1352,7 +1296,7 @@
         <v>19</v>
       </c>
       <c r="F19" s="4">
-        <v>45964</v>
+        <v>45993</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>20</v>
@@ -1361,18 +1305,18 @@
         <v>21</v>
       </c>
       <c r="I19" s="3">
-        <v>1800095</v>
+        <v>2003550</v>
       </c>
       <c r="J19" s="3">
-        <v>1800095</v>
+        <v>2003550</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>17</v>
@@ -1381,10 +1325,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F20" s="4">
-        <v>45966</v>
+        <v>45993</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>20</v>
@@ -1393,18 +1337,18 @@
         <v>21</v>
       </c>
       <c r="I20" s="3">
-        <v>380512</v>
+        <v>94905</v>
       </c>
       <c r="J20" s="3">
-        <v>380512</v>
+        <v>94905</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>17</v>
@@ -1413,10 +1357,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F21" s="4">
-        <v>45966</v>
+        <v>45993</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>20</v>
@@ -1425,18 +1369,18 @@
         <v>21</v>
       </c>
       <c r="I21" s="3">
-        <v>197435</v>
+        <v>208125</v>
       </c>
       <c r="J21" s="3">
-        <v>195727</v>
+        <v>208125</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>17</v>
@@ -1445,10 +1389,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="F22" s="4">
-        <v>45966</v>
+        <v>45993</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>20</v>
@@ -1457,18 +1401,18 @@
         <v>21</v>
       </c>
       <c r="I22" s="3">
-        <v>380512</v>
+        <v>324675</v>
       </c>
       <c r="J22" s="3">
-        <v>33504</v>
+        <v>324675</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>17</v>
@@ -1477,10 +1421,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F23" s="4">
-        <v>45966</v>
+        <v>45993</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>20</v>
@@ -1489,30 +1433,30 @@
         <v>21</v>
       </c>
       <c r="I23" s="3">
-        <v>197435</v>
+        <v>94905</v>
       </c>
       <c r="J23" s="3">
-        <v>37740</v>
+        <v>94905</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F24" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>20</v>
@@ -1521,30 +1465,30 @@
         <v>21</v>
       </c>
       <c r="I24" s="3">
-        <v>47452</v>
+        <v>604395</v>
       </c>
       <c r="J24" s="3">
-        <v>47452</v>
+        <v>604395</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F25" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>20</v>
@@ -1553,30 +1497,30 @@
         <v>21</v>
       </c>
       <c r="I25" s="3">
-        <v>789210</v>
+        <v>1254300</v>
       </c>
       <c r="J25" s="3">
-        <v>789210</v>
+        <v>1254300</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F26" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>20</v>
@@ -1585,30 +1529,30 @@
         <v>21</v>
       </c>
       <c r="I26" s="3">
-        <v>108225</v>
+        <v>3330000</v>
       </c>
       <c r="J26" s="3">
-        <v>108225</v>
+        <v>3330000</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F27" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>20</v>
@@ -1617,30 +1561,30 @@
         <v>21</v>
       </c>
       <c r="I27" s="3">
-        <v>201465</v>
+        <v>4162500</v>
       </c>
       <c r="J27" s="3">
-        <v>201465</v>
+        <v>4162500</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F28" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>20</v>
@@ -1649,30 +1593,30 @@
         <v>21</v>
       </c>
       <c r="I28" s="3">
-        <v>1864800</v>
+        <v>53537</v>
       </c>
       <c r="J28" s="3">
-        <v>1864800</v>
+        <v>53537</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F29" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>20</v>
@@ -1681,30 +1625,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="3">
-        <v>213120</v>
+        <v>1491007</v>
       </c>
       <c r="J29" s="3">
-        <v>213120</v>
+        <v>1491007</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F30" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>20</v>
@@ -1713,30 +1657,30 @@
         <v>21</v>
       </c>
       <c r="I30" s="3">
-        <v>979075</v>
+        <v>162504</v>
       </c>
       <c r="J30" s="3">
-        <v>979075</v>
+        <v>162504</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F31" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>20</v>
@@ -1745,30 +1689,30 @@
         <v>21</v>
       </c>
       <c r="I31" s="3">
-        <v>266400</v>
+        <v>453550</v>
       </c>
       <c r="J31" s="3">
-        <v>266400</v>
+        <v>453550</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F32" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>20</v>
@@ -1777,30 +1721,30 @@
         <v>21</v>
       </c>
       <c r="I32" s="3">
-        <v>1065600</v>
+        <v>557308</v>
       </c>
       <c r="J32" s="3">
-        <v>1065600</v>
+        <v>557308</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F33" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>20</v>
@@ -1809,30 +1753,30 @@
         <v>21</v>
       </c>
       <c r="I33" s="3">
-        <v>31635</v>
+        <v>201465</v>
       </c>
       <c r="J33" s="3">
-        <v>31635</v>
+        <v>201465</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F34" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>20</v>
@@ -1841,30 +1785,30 @@
         <v>21</v>
       </c>
       <c r="I34" s="3">
-        <v>47452</v>
+        <v>2278830</v>
       </c>
       <c r="J34" s="3">
-        <v>47452</v>
+        <v>2278830</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F35" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>20</v>
@@ -1873,30 +1817,30 @@
         <v>21</v>
       </c>
       <c r="I35" s="3">
-        <v>926295</v>
+        <v>55444</v>
       </c>
       <c r="J35" s="3">
-        <v>926295</v>
+        <v>55444</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F36" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>20</v>
@@ -1905,30 +1849,30 @@
         <v>21</v>
       </c>
       <c r="I36" s="3">
-        <v>1864800</v>
+        <v>158175</v>
       </c>
       <c r="J36" s="3">
-        <v>1864800</v>
+        <v>158175</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F37" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>20</v>
@@ -1937,30 +1881,30 @@
         <v>21</v>
       </c>
       <c r="I37" s="3">
-        <v>555000</v>
+        <v>31635</v>
       </c>
       <c r="J37" s="3">
-        <v>555000</v>
+        <v>31635</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F38" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>20</v>
@@ -1969,30 +1913,30 @@
         <v>21</v>
       </c>
       <c r="I38" s="3">
-        <v>532800</v>
+        <v>11721</v>
       </c>
       <c r="J38" s="3">
-        <v>532800</v>
+        <v>11721</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F39" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>20</v>
@@ -2001,30 +1945,30 @@
         <v>21</v>
       </c>
       <c r="I39" s="3">
-        <v>1010100</v>
+        <v>213120</v>
       </c>
       <c r="J39" s="3">
-        <v>1010100</v>
+        <v>213120</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F40" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>20</v>
@@ -2033,30 +1977,30 @@
         <v>21</v>
       </c>
       <c r="I40" s="3">
-        <v>138750</v>
+        <v>454545</v>
       </c>
       <c r="J40" s="3">
-        <v>138750</v>
+        <v>454545</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F41" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>20</v>
@@ -2065,30 +2009,30 @@
         <v>21</v>
       </c>
       <c r="I41" s="3">
-        <v>111055</v>
+        <v>117981</v>
       </c>
       <c r="J41" s="3">
-        <v>111055</v>
+        <v>117981</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F42" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>20</v>
@@ -2097,30 +2041,30 @@
         <v>21</v>
       </c>
       <c r="I42" s="3">
-        <v>144300</v>
+        <v>948550</v>
       </c>
       <c r="J42" s="3">
-        <v>144300</v>
+        <v>948550</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F43" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>20</v>
@@ -2129,30 +2073,30 @@
         <v>21</v>
       </c>
       <c r="I43" s="3">
-        <v>2024640</v>
+        <v>1526250</v>
       </c>
       <c r="J43" s="3">
-        <v>2024640</v>
+        <v>1526250</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="F44" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>20</v>
@@ -2161,30 +2105,30 @@
         <v>21</v>
       </c>
       <c r="I44" s="3">
-        <v>308726</v>
+        <v>4528800</v>
       </c>
       <c r="J44" s="3">
-        <v>308726</v>
+        <v>4528800</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F45" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>20</v>
@@ -2193,30 +2137,30 @@
         <v>21</v>
       </c>
       <c r="I45" s="3">
-        <v>31635</v>
+        <v>213120</v>
       </c>
       <c r="J45" s="3">
-        <v>31635</v>
+        <v>213120</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F46" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>20</v>
@@ -2225,30 +2169,30 @@
         <v>21</v>
       </c>
       <c r="I46" s="3">
-        <v>109890</v>
+        <v>805860</v>
       </c>
       <c r="J46" s="3">
-        <v>109890</v>
+        <v>805860</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F47" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>20</v>
@@ -2257,30 +2201,30 @@
         <v>21</v>
       </c>
       <c r="I47" s="3">
-        <v>430015</v>
+        <v>1192806</v>
       </c>
       <c r="J47" s="3">
-        <v>430015</v>
+        <v>1192806</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F48" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>20</v>
@@ -2289,30 +2233,30 @@
         <v>21</v>
       </c>
       <c r="I48" s="3">
-        <v>138750</v>
+        <v>266400</v>
       </c>
       <c r="J48" s="3">
-        <v>138750</v>
+        <v>266400</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F49" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>20</v>
@@ -2321,30 +2265,30 @@
         <v>21</v>
       </c>
       <c r="I49" s="3">
-        <v>639360</v>
+        <v>72150</v>
       </c>
       <c r="J49" s="3">
-        <v>639360</v>
+        <v>72150</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F50" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>20</v>
@@ -2353,30 +2297,30 @@
         <v>21</v>
       </c>
       <c r="I50" s="3">
-        <v>2150625</v>
+        <v>201465</v>
       </c>
       <c r="J50" s="3">
-        <v>2150625</v>
+        <v>201465</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F51" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>20</v>
@@ -2385,30 +2329,30 @@
         <v>21</v>
       </c>
       <c r="I51" s="3">
-        <v>222027</v>
+        <v>106893</v>
       </c>
       <c r="J51" s="3">
-        <v>222027</v>
+        <v>106893</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F52" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>20</v>
@@ -2417,30 +2361,30 @@
         <v>21</v>
       </c>
       <c r="I52" s="3">
-        <v>394605</v>
+        <v>201465</v>
       </c>
       <c r="J52" s="3">
-        <v>394605</v>
+        <v>201465</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F53" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>20</v>
@@ -2449,30 +2393,30 @@
         <v>21</v>
       </c>
       <c r="I53" s="3">
-        <v>104895</v>
+        <v>1672215</v>
       </c>
       <c r="J53" s="3">
-        <v>104895</v>
+        <v>1672215</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="F54" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>20</v>
@@ -2481,30 +2425,30 @@
         <v>21</v>
       </c>
       <c r="I54" s="3">
-        <v>224775</v>
+        <v>74925</v>
       </c>
       <c r="J54" s="3">
-        <v>224775</v>
+        <v>74925</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="F55" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>20</v>
@@ -2513,30 +2457,30 @@
         <v>21</v>
       </c>
       <c r="I55" s="3">
-        <v>1887000</v>
+        <v>7002213</v>
       </c>
       <c r="J55" s="3">
-        <v>1887000</v>
+        <v>7002213</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="F56" s="4">
-        <v>45966</v>
+        <v>45993</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>20</v>
@@ -2545,30 +2489,30 @@
         <v>21</v>
       </c>
       <c r="I56" s="3">
-        <v>1818653</v>
+        <v>3312795</v>
       </c>
       <c r="J56" s="3">
-        <v>1818653</v>
+        <v>3312795</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F57" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>20</v>
@@ -2577,30 +2521,30 @@
         <v>21</v>
       </c>
       <c r="I57" s="3">
-        <v>2316718</v>
+        <v>569430</v>
       </c>
       <c r="J57" s="3">
-        <v>2316718</v>
+        <v>569430</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F58" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>20</v>
@@ -2609,30 +2553,30 @@
         <v>21</v>
       </c>
       <c r="I58" s="3">
-        <v>3731814</v>
+        <v>31635</v>
       </c>
       <c r="J58" s="3">
-        <v>3731814</v>
+        <v>31635</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="F59" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>20</v>
@@ -2641,30 +2585,30 @@
         <v>21</v>
       </c>
       <c r="I59" s="3">
-        <v>1751802</v>
+        <v>497002</v>
       </c>
       <c r="J59" s="3">
-        <v>1751802</v>
+        <v>497002</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F60" s="4">
-        <v>45975</v>
+        <v>45966</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>20</v>
@@ -2673,30 +2617,30 @@
         <v>21</v>
       </c>
       <c r="I60" s="3">
-        <v>1278720</v>
+        <v>380512</v>
       </c>
       <c r="J60" s="3">
-        <v>1278720</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F61" s="4">
-        <v>45975</v>
+        <v>45966</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>20</v>
@@ -2705,30 +2649,30 @@
         <v>21</v>
       </c>
       <c r="I61" s="3">
-        <v>10516015</v>
+        <v>197435</v>
       </c>
       <c r="J61" s="3">
-        <v>10516015</v>
+        <v>195727</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="F62" s="4">
-        <v>45975</v>
+        <v>45966</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>20</v>
@@ -2737,30 +2681,30 @@
         <v>21</v>
       </c>
       <c r="I62" s="3">
-        <v>922211</v>
+        <v>380512</v>
       </c>
       <c r="J62" s="3">
-        <v>922211</v>
+        <v>33504</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="F63" s="4">
-        <v>45971</v>
+        <v>45986</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>20</v>
@@ -2769,30 +2713,30 @@
         <v>21</v>
       </c>
       <c r="I63" s="3">
-        <v>11982608</v>
+        <v>2095198</v>
       </c>
       <c r="J63" s="3">
-        <v>11982608</v>
+        <v>489596</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="F64" s="4">
-        <v>45971</v>
+        <v>45966</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>20</v>
@@ -2801,30 +2745,30 @@
         <v>21</v>
       </c>
       <c r="I64" s="3">
-        <v>3007975</v>
+        <v>197435</v>
       </c>
       <c r="J64" s="3">
-        <v>3007975</v>
+        <v>37740</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="F65" s="4">
-        <v>45971</v>
+        <v>45992</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>20</v>
@@ -2833,30 +2777,30 @@
         <v>21</v>
       </c>
       <c r="I65" s="3">
-        <v>1081237</v>
+        <v>706826</v>
       </c>
       <c r="J65" s="3">
-        <v>1081237</v>
+        <v>82450</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F66" s="4">
-        <v>45971</v>
+        <v>45993</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>20</v>
@@ -2865,94 +2809,94 @@
         <v>21</v>
       </c>
       <c r="I66" s="3">
-        <v>2697566</v>
+        <v>897083</v>
       </c>
       <c r="J66" s="3">
-        <v>2697566</v>
+        <v>897083</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F67" s="4">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="I67" s="3">
-        <v>-37773</v>
+        <v>607392</v>
       </c>
       <c r="J67" s="3">
-        <v>-37773</v>
+        <v>607392</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F68" s="4">
-        <v>45972</v>
+        <v>45993</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>117</v>
+        <v>21</v>
       </c>
       <c r="I68" s="3">
-        <v>-126318</v>
+        <v>2838067</v>
       </c>
       <c r="J68" s="3">
-        <v>-126318</v>
+        <v>2838067</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>17</v>
+        <v>98</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F69" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>20</v>
@@ -2961,30 +2905,30 @@
         <v>21</v>
       </c>
       <c r="I69" s="3">
-        <v>1056153</v>
+        <v>491508</v>
       </c>
       <c r="J69" s="3">
-        <v>1056153</v>
+        <v>491508</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>122</v>
+        <v>19</v>
       </c>
       <c r="F70" s="4">
-        <v>45974</v>
+        <v>45986</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>20</v>
@@ -2993,30 +2937,30 @@
         <v>21</v>
       </c>
       <c r="I70" s="3">
-        <v>2095198</v>
+        <v>744028</v>
       </c>
       <c r="J70" s="3">
-        <v>2095198</v>
+        <v>744028</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="F71" s="4">
-        <v>45974</v>
+        <v>45993</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>20</v>
@@ -3025,30 +2969,30 @@
         <v>21</v>
       </c>
       <c r="I71" s="3">
-        <v>9926119</v>
+        <v>15244365</v>
       </c>
       <c r="J71" s="3">
-        <v>9926119</v>
+        <v>14737723</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="F72" s="4">
-        <v>45974</v>
+        <v>45988</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>20</v>
@@ -3057,30 +3001,30 @@
         <v>21</v>
       </c>
       <c r="I72" s="3">
-        <v>11788072</v>
+        <v>270004</v>
       </c>
       <c r="J72" s="3">
-        <v>5898744</v>
+        <v>100004</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="F73" s="4">
-        <v>45964</v>
+        <v>45988</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>20</v>
@@ -3089,30 +3033,30 @@
         <v>21</v>
       </c>
       <c r="I73" s="3">
-        <v>380512</v>
+        <v>261008</v>
       </c>
       <c r="J73" s="3">
-        <v>380512</v>
+        <v>75000</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="F74" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>20</v>
@@ -3121,30 +3065,30 @@
         <v>21</v>
       </c>
       <c r="I74" s="3">
-        <v>402050</v>
+        <v>197435</v>
       </c>
       <c r="J74" s="3">
-        <v>402050</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="F75" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>20</v>
@@ -3153,30 +3097,30 @@
         <v>21</v>
       </c>
       <c r="I75" s="3">
-        <v>197435</v>
+        <v>979999</v>
       </c>
       <c r="J75" s="3">
-        <v>197435</v>
+        <v>979999</v>
       </c>
     </row>
     <row r="76" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="F76" s="4">
-        <v>45975</v>
+        <v>45993</v>
       </c>
       <c r="G76" s="3" t="s">
         <v>20</v>
@@ -3193,22 +3137,22 @@
     </row>
     <row r="77" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F77" s="4">
-        <v>45975</v>
+        <v>45992</v>
       </c>
       <c r="G77" s="3" t="s">
         <v>20</v>
@@ -3217,30 +3161,30 @@
         <v>21</v>
       </c>
       <c r="I77" s="3">
-        <v>197435</v>
+        <v>1916921</v>
       </c>
       <c r="J77" s="3">
-        <v>197435</v>
+        <v>1916921</v>
       </c>
     </row>
     <row r="78" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F78" s="4">
-        <v>45975</v>
+        <v>45992</v>
       </c>
       <c r="G78" s="3" t="s">
         <v>20</v>
@@ -3249,30 +3193,30 @@
         <v>21</v>
       </c>
       <c r="I78" s="3">
-        <v>2095198</v>
+        <v>380512</v>
       </c>
       <c r="J78" s="3">
-        <v>2095198</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="79" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="F79" s="4">
-        <v>45975</v>
+        <v>45992</v>
       </c>
       <c r="G79" s="3" t="s">
         <v>20</v>
@@ -3281,30 +3225,30 @@
         <v>21</v>
       </c>
       <c r="I79" s="3">
-        <v>941626</v>
+        <v>1474407</v>
       </c>
       <c r="J79" s="3">
-        <v>941626</v>
+        <v>1474407</v>
       </c>
     </row>
     <row r="80" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F80" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G80" s="3" t="s">
         <v>20</v>
@@ -3313,30 +3257,30 @@
         <v>21</v>
       </c>
       <c r="I80" s="3">
-        <v>1078388</v>
+        <v>599486</v>
       </c>
       <c r="J80" s="3">
-        <v>1078388</v>
+        <v>599486</v>
       </c>
     </row>
     <row r="81" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F81" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>20</v>
@@ -3345,30 +3289,30 @@
         <v>21</v>
       </c>
       <c r="I81" s="3">
-        <v>402050</v>
+        <v>380512</v>
       </c>
       <c r="J81" s="3">
-        <v>402050</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="82" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="C82" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F82" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G82" s="3" t="s">
         <v>20</v>
@@ -3377,30 +3321,30 @@
         <v>21</v>
       </c>
       <c r="I82" s="3">
-        <v>197435</v>
+        <v>706826</v>
       </c>
       <c r="J82" s="3">
-        <v>197435</v>
+        <v>706826</v>
       </c>
     </row>
     <row r="83" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F83" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G83" s="3" t="s">
         <v>20</v>
@@ -3409,30 +3353,30 @@
         <v>21</v>
       </c>
       <c r="I83" s="3">
-        <v>197435</v>
+        <v>4190395</v>
       </c>
       <c r="J83" s="3">
-        <v>197435</v>
+        <v>4190395</v>
       </c>
     </row>
     <row r="84" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F84" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G84" s="3" t="s">
         <v>20</v>
@@ -3441,30 +3385,30 @@
         <v>21</v>
       </c>
       <c r="I84" s="3">
-        <v>380512</v>
+        <v>12990219</v>
       </c>
       <c r="J84" s="3">
-        <v>380512</v>
+        <v>12990219</v>
       </c>
     </row>
     <row r="85" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F85" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G85" s="3" t="s">
         <v>20</v>
@@ -3473,30 +3417,30 @@
         <v>21</v>
       </c>
       <c r="I85" s="3">
-        <v>175000</v>
+        <v>380512</v>
       </c>
       <c r="J85" s="3">
-        <v>175000</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="86" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>24</v>
+        <v>83</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F86" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G86" s="3" t="s">
         <v>20</v>
@@ -3505,30 +3449,30 @@
         <v>21</v>
       </c>
       <c r="I86" s="3">
-        <v>144550</v>
+        <v>197435</v>
       </c>
       <c r="J86" s="3">
-        <v>144550</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="87" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
       <c r="F87" s="4">
-        <v>45974</v>
+        <v>45989</v>
       </c>
       <c r="G87" s="3" t="s">
         <v>20</v>
@@ -3537,30 +3481,30 @@
         <v>21</v>
       </c>
       <c r="I87" s="3">
-        <v>133200</v>
+        <v>2020014</v>
       </c>
       <c r="J87" s="3">
-        <v>133200</v>
+        <v>2020014</v>
       </c>
     </row>
     <row r="88" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F88" s="4">
-        <v>45975</v>
+        <v>45990</v>
       </c>
       <c r="G88" s="3" t="s">
         <v>20</v>
@@ -3569,170 +3513,10 @@
         <v>21</v>
       </c>
       <c r="I88" s="3">
-        <v>355200</v>
+        <v>532800</v>
       </c>
       <c r="J88" s="3">
-        <v>355200</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A89" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F89" s="4">
-        <v>45974</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I89" s="3">
-        <v>1348650</v>
-      </c>
-      <c r="J89" s="3">
-        <v>1348650</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A90" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F90" s="4">
-        <v>45974</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I90" s="3">
-        <v>333000</v>
-      </c>
-      <c r="J90" s="3">
-        <v>333000</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A91" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C91" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F91" s="4">
-        <v>45974</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I91" s="3">
-        <v>700683</v>
-      </c>
-      <c r="J91" s="3">
-        <v>700683</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A92" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F92" s="4">
-        <v>45974</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I92" s="3">
-        <v>368181</v>
-      </c>
-      <c r="J92" s="3">
-        <v>368181</v>
-      </c>
-    </row>
-    <row r="93" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A93" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="F93" s="4">
-        <v>45974</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I93" s="3">
-        <v>183072</v>
-      </c>
-      <c r="J93" s="3">
-        <v>183072</v>
+        <v>532800</v>
       </c>
     </row>
   </sheetData>

--- a/uploads/transfer.xlsx
+++ b/uploads/transfer.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\coralis\20251202\fix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Coralis\Eksport Implementasi\20251215\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29613FC0-3F95-4423-A7E3-B2FAF9233AEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12585"/>
   </bookViews>
   <sheets>
     <sheet name="Intransit Transfer Outstanding" sheetId="1" r:id="rId1"/>
@@ -20,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="615" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="139">
   <si>
     <t>nomor_request</t>
   </si>
@@ -67,397 +66,382 @@
     <t>ex: angka</t>
   </si>
   <si>
-    <t>0826ACH25000039</t>
-  </si>
-  <si>
-    <t>08ASB25018184</t>
+    <t>2526ACH25000118</t>
+  </si>
+  <si>
+    <t>25ASB25020312</t>
+  </si>
+  <si>
+    <t>TANGERANG</t>
+  </si>
+  <si>
+    <t>BEKASI</t>
+  </si>
+  <si>
+    <t>TF RSU MITRA KALIDERES</t>
+  </si>
+  <si>
+    <t>Intransit</t>
+  </si>
+  <si>
+    <t>OUTSTANDING</t>
+  </si>
+  <si>
+    <t>25ASB25020313</t>
+  </si>
+  <si>
+    <t>25ASB25020314</t>
+  </si>
+  <si>
+    <t>25ASB25020315</t>
+  </si>
+  <si>
+    <t>2826ACH25000016</t>
+  </si>
+  <si>
+    <t>26ASB25020250</t>
+  </si>
+  <si>
+    <t>PUSAT (PIUTANG)</t>
+  </si>
+  <si>
+    <t>POT RETUR WATSON BKS KPO 16.10.2025</t>
+  </si>
+  <si>
+    <t>26ASB25020251</t>
+  </si>
+  <si>
+    <t>27ASB25014375</t>
+  </si>
+  <si>
+    <t>0827ACH25000028</t>
+  </si>
+  <si>
+    <t>08ASB25017561</t>
   </si>
   <si>
     <t>BOGOR</t>
   </si>
   <si>
-    <t>BEKASI</t>
+    <t>JAKARTA SELATAN</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>Intransit</t>
-  </si>
-  <si>
-    <t>OUTSTANDING</t>
-  </si>
-  <si>
-    <t>08ASB25018185</t>
-  </si>
-  <si>
-    <t>08ASB25018186</t>
-  </si>
-  <si>
-    <t>08ASB25018187</t>
-  </si>
-  <si>
-    <t>08ASB25018188</t>
-  </si>
-  <si>
-    <t>08ASB25018191</t>
-  </si>
-  <si>
-    <t>08ASB25018192</t>
-  </si>
-  <si>
-    <t>08ASB25018193</t>
-  </si>
-  <si>
-    <t>08ASB25018195</t>
-  </si>
-  <si>
-    <t>08ASB25018250</t>
-  </si>
-  <si>
-    <t>08ASB25018275</t>
-  </si>
-  <si>
-    <t>08ASB25018276</t>
-  </si>
-  <si>
-    <t>08ASB25018277</t>
-  </si>
-  <si>
-    <t>08ASB25018286</t>
-  </si>
-  <si>
-    <t>08ASB25018287</t>
-  </si>
-  <si>
-    <t>08ASB25018301</t>
-  </si>
-  <si>
-    <t>08ASB25018373</t>
-  </si>
-  <si>
-    <t>08ASB25018387</t>
-  </si>
-  <si>
-    <t>08ASB25018388</t>
-  </si>
-  <si>
-    <t>08ASB25018403</t>
-  </si>
-  <si>
-    <t>08ASB25018404</t>
-  </si>
-  <si>
-    <t>08ASB25018405</t>
-  </si>
-  <si>
-    <t>08ASB25018406</t>
-  </si>
-  <si>
-    <t>08ASB25018407</t>
-  </si>
-  <si>
-    <t>08ASB25018445</t>
-  </si>
-  <si>
-    <t>08ASB25018467</t>
-  </si>
-  <si>
-    <t>08ASB25018471</t>
-  </si>
-  <si>
-    <t>08ASB25018472</t>
-  </si>
-  <si>
-    <t>08ASB25018515</t>
-  </si>
-  <si>
-    <t>08ASB25018521</t>
-  </si>
-  <si>
-    <t>08ASB25018522</t>
-  </si>
-  <si>
-    <t>08ASB25018524</t>
-  </si>
-  <si>
-    <t>08ASB25018586</t>
-  </si>
-  <si>
-    <t>08ASB25018596</t>
-  </si>
-  <si>
-    <t>08ASB25018597</t>
-  </si>
-  <si>
-    <t>08ASB25018622</t>
-  </si>
-  <si>
-    <t>08ASB25018623</t>
-  </si>
-  <si>
-    <t>08ASB25018628</t>
-  </si>
-  <si>
-    <t>08ASB25018629</t>
-  </si>
-  <si>
-    <t>08ASB25018630</t>
-  </si>
-  <si>
-    <t>08ASB25018631</t>
-  </si>
-  <si>
-    <t>08ASB25018632</t>
-  </si>
-  <si>
-    <t>08ASB25018633</t>
-  </si>
-  <si>
-    <t>08ASB25018641</t>
-  </si>
-  <si>
-    <t>08ASB25018694</t>
-  </si>
-  <si>
-    <t>08ASB25018695</t>
-  </si>
-  <si>
-    <t>08ASB25018696</t>
-  </si>
-  <si>
-    <t>08ASB25018697</t>
-  </si>
-  <si>
-    <t>08ASB25018698</t>
-  </si>
-  <si>
-    <t>08ASB25018699</t>
-  </si>
-  <si>
-    <t>0826BCH25000014</t>
-  </si>
-  <si>
-    <t>08BSB25001003</t>
-  </si>
-  <si>
-    <t>2526ACH25000114</t>
-  </si>
-  <si>
-    <t>25ASB25019605</t>
-  </si>
-  <si>
-    <t>TANGERANG</t>
-  </si>
-  <si>
-    <t>TF MITRA KALIDERES DI BEKASI</t>
-  </si>
-  <si>
-    <t>25ASB25019606</t>
-  </si>
-  <si>
-    <t>25ASB25019647</t>
-  </si>
-  <si>
-    <t>25ASB25019664</t>
-  </si>
-  <si>
-    <t>25ASB25019764</t>
-  </si>
-  <si>
-    <t>2826ACH25000016</t>
-  </si>
-  <si>
-    <t>26ASB25020250</t>
-  </si>
-  <si>
-    <t>PUSAT (PIUTANG)</t>
-  </si>
-  <si>
-    <t>POT RETUR WATSON BKS KPO 16.10.2025</t>
-  </si>
-  <si>
-    <t>26ASB25020251</t>
-  </si>
-  <si>
-    <t>2826ACH25000017</t>
-  </si>
-  <si>
-    <t>26ASB25021228</t>
-  </si>
-  <si>
-    <t>POT RETUR WATSON BKS KPO 27.10.2025</t>
-  </si>
-  <si>
-    <t>2826ACH25000018</t>
-  </si>
-  <si>
-    <t>26ASB25026401</t>
-  </si>
-  <si>
-    <t>POT RETUR TIPTOP BKS GIRO 717952</t>
-  </si>
-  <si>
-    <t>27ASB25014375</t>
-  </si>
-  <si>
-    <t>2808ACH25000009</t>
-  </si>
-  <si>
-    <t>07ASB25031653</t>
-  </si>
-  <si>
-    <t>POT RETUR TIPTOP BCA 05.11.2025</t>
-  </si>
-  <si>
-    <t>0727ACH25000111</t>
-  </si>
-  <si>
-    <t>07ASB25037663</t>
+    <t>2627ACH25000093</t>
+  </si>
+  <si>
+    <t>26ASB25029576</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>26ASB25029868</t>
+  </si>
+  <si>
+    <t>26ASB25030030</t>
+  </si>
+  <si>
+    <t>2627ACH25000094</t>
+  </si>
+  <si>
+    <t>26ASB25030243</t>
+  </si>
+  <si>
+    <t>TUKAR FAKTUR DI JAKSEL</t>
+  </si>
+  <si>
+    <t>0700ACH25000066</t>
+  </si>
+  <si>
+    <t>07ASB25037678</t>
   </si>
   <si>
     <t>JAKARTA PUSAT</t>
   </si>
   <si>
-    <t>JAKARTA SELATAN</t>
-  </si>
-  <si>
-    <t>TF DI SELATAN</t>
-  </si>
-  <si>
-    <t>07ASB25037742</t>
-  </si>
-  <si>
-    <t>07ASB25038078</t>
-  </si>
-  <si>
-    <t>07ASB25038091</t>
-  </si>
-  <si>
-    <t>0827ACH25000028</t>
-  </si>
-  <si>
-    <t>08ASB25017561</t>
-  </si>
-  <si>
-    <t>0700ACH25000063</t>
-  </si>
-  <si>
-    <t>07ASB25037908</t>
-  </si>
-  <si>
     <t>KANTOR PUSAT</t>
   </si>
   <si>
-    <t>POT RAFRAKSI</t>
-  </si>
-  <si>
-    <t>1600ACH25000007</t>
-  </si>
-  <si>
-    <t>16ASB25020042</t>
+    <t>SISA POT RAFRAKSI</t>
+  </si>
+  <si>
+    <t>0700ACH25000065</t>
+  </si>
+  <si>
+    <t>25ASB25017112</t>
+  </si>
+  <si>
+    <t>RAFAKSI ET</t>
+  </si>
+  <si>
+    <t>2600ACH25000022</t>
+  </si>
+  <si>
+    <t>26ASB25026652</t>
+  </si>
+  <si>
+    <t>RAFRAKSI NOVEMBER 2025</t>
+  </si>
+  <si>
+    <t>2800ACH25000084</t>
+  </si>
+  <si>
+    <t>27ASB25019462</t>
+  </si>
+  <si>
+    <t>POT PROG FOODHALL 19609 BCA 10.12.2025</t>
+  </si>
+  <si>
+    <t>0728ACH25000199</t>
+  </si>
+  <si>
+    <t>07ASB25039702</t>
+  </si>
+  <si>
+    <t>07ASB25039766</t>
+  </si>
+  <si>
+    <t>07ASB25039840</t>
+  </si>
+  <si>
+    <t>07ASB25039862</t>
+  </si>
+  <si>
+    <t>0728ACH25000200</t>
+  </si>
+  <si>
+    <t>07ASB25039974</t>
+  </si>
+  <si>
+    <t>07ASB25039976</t>
+  </si>
+  <si>
+    <t>07ASB25039977</t>
+  </si>
+  <si>
+    <t>07ASB25039978</t>
+  </si>
+  <si>
+    <t>07ASB25040010</t>
+  </si>
+  <si>
+    <t>07ASB25040025</t>
+  </si>
+  <si>
+    <t>07ASB25040026</t>
+  </si>
+  <si>
+    <t>07ASB25040033</t>
+  </si>
+  <si>
+    <t>0828ACH25000045</t>
+  </si>
+  <si>
+    <t>08ASB25019373</t>
+  </si>
+  <si>
+    <t>08ASB25019665</t>
+  </si>
+  <si>
+    <t>08ASB25019737</t>
+  </si>
+  <si>
+    <t>08ASB25019845</t>
+  </si>
+  <si>
+    <t>08ASB25019889</t>
+  </si>
+  <si>
+    <t>08ASB25019908</t>
+  </si>
+  <si>
+    <t>0928ACH25000025</t>
+  </si>
+  <si>
+    <t>09ASB25024418</t>
+  </si>
+  <si>
+    <t>BANDUNG</t>
+  </si>
+  <si>
+    <t>1128ACH25000012</t>
+  </si>
+  <si>
+    <t>11ASB25036258</t>
+  </si>
+  <si>
+    <t>SEMARANG</t>
+  </si>
+  <si>
+    <t>1228ACH25000005</t>
+  </si>
+  <si>
+    <t>12ASB25024851</t>
+  </si>
+  <si>
+    <t>SOLO</t>
+  </si>
+  <si>
+    <t>1628ACH25000022</t>
+  </si>
+  <si>
+    <t>16ASB25023355</t>
   </si>
   <si>
     <t>DENPASAR</t>
   </si>
   <si>
-    <t>PENGALIHAN POT LISTING</t>
-  </si>
-  <si>
-    <t>16ASB25020402</t>
-  </si>
-  <si>
-    <t>0228ACH25000011</t>
-  </si>
-  <si>
-    <t>02ASB25020598</t>
-  </si>
-  <si>
-    <t>MEDAN</t>
-  </si>
-  <si>
-    <t>FAKTUR WATSONS MANHATTAN 29/11/25</t>
-  </si>
-  <si>
-    <t>0728ACH25000193</t>
-  </si>
-  <si>
-    <t>07ASB25038512</t>
-  </si>
-  <si>
-    <t>TF DI PUSAT</t>
-  </si>
-  <si>
-    <t>2328ACH25000028</t>
-  </si>
-  <si>
-    <t>23ASB25012778</t>
+    <t>16ASB25023788</t>
+  </si>
+  <si>
+    <t>2528ACH25000094</t>
+  </si>
+  <si>
+    <t>25ASB25020055</t>
+  </si>
+  <si>
+    <t>TUKER FAKTUR DI PUSAT</t>
+  </si>
+  <si>
+    <t>25ASB25020440</t>
+  </si>
+  <si>
+    <t>2528ACH25000095</t>
+  </si>
+  <si>
+    <t>25ASB25020493</t>
+  </si>
+  <si>
+    <t>TUKAR FAKTUR DI PUSAT</t>
+  </si>
+  <si>
+    <t>25ASB25020506</t>
+  </si>
+  <si>
+    <t>25ASB25020517</t>
+  </si>
+  <si>
+    <t>2628ACH25000051</t>
+  </si>
+  <si>
+    <t>26ASB25028423</t>
+  </si>
+  <si>
+    <t>26ASB25028424</t>
+  </si>
+  <si>
+    <t>26ASB25028425</t>
+  </si>
+  <si>
+    <t>26ASB25028475</t>
+  </si>
+  <si>
+    <t>26ASB25028617</t>
+  </si>
+  <si>
+    <t>26ASB25028735</t>
+  </si>
+  <si>
+    <t>26ASB25028736</t>
+  </si>
+  <si>
+    <t>26ASB25028737</t>
+  </si>
+  <si>
+    <t>26ASB25029099</t>
+  </si>
+  <si>
+    <t>26ASB25029100</t>
+  </si>
+  <si>
+    <t>26ASB25029101</t>
+  </si>
+  <si>
+    <t>26ASB25029102</t>
+  </si>
+  <si>
+    <t>26ASB25029103</t>
+  </si>
+  <si>
+    <t>26ASB25029392</t>
+  </si>
+  <si>
+    <t>26ASB25029396</t>
+  </si>
+  <si>
+    <t>26ASB25029593</t>
+  </si>
+  <si>
+    <t>26ASB25029651</t>
+  </si>
+  <si>
+    <t>26ASB25029652</t>
+  </si>
+  <si>
+    <t>26ASB25029653</t>
+  </si>
+  <si>
+    <t>26ASB25029654</t>
+  </si>
+  <si>
+    <t>26ASB25029658</t>
+  </si>
+  <si>
+    <t>26ASB25029753</t>
+  </si>
+  <si>
+    <t>26ASB25029754</t>
+  </si>
+  <si>
+    <t>26ASB25029755</t>
+  </si>
+  <si>
+    <t>26ASB25029836</t>
+  </si>
+  <si>
+    <t>0421ACH25000066</t>
+  </si>
+  <si>
+    <t>04ASB25011832</t>
+  </si>
+  <si>
+    <t>JAMBI</t>
+  </si>
+  <si>
+    <t>PUSAT 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPN BATAL </t>
+  </si>
+  <si>
+    <t>1823BCH25000002</t>
+  </si>
+  <si>
+    <t>18BSB25000217</t>
+  </si>
+  <si>
+    <t>PUSAT 79</t>
   </si>
   <si>
     <t>SAMARINDA</t>
   </si>
   <si>
-    <t>2528ACH25000090</t>
-  </si>
-  <si>
-    <t>25ASB25019194</t>
-  </si>
-  <si>
-    <t>TUKER FAKTUR DI PUSAT</t>
-  </si>
-  <si>
-    <t>25ASB25019608</t>
-  </si>
-  <si>
-    <t>25ASB25019692</t>
-  </si>
-  <si>
-    <t>2728ACH25000052</t>
-  </si>
-  <si>
-    <t>27ASB25020868</t>
-  </si>
-  <si>
-    <t>HARI HARI, TIP TOP, DAN WATSONS</t>
-  </si>
-  <si>
-    <t>27ASB25020871</t>
-  </si>
-  <si>
-    <t>27ASB25021039</t>
-  </si>
-  <si>
-    <t>27ASB25021066</t>
-  </si>
-  <si>
-    <t>27ASB25021282</t>
-  </si>
-  <si>
-    <t>27ASB25021376</t>
-  </si>
-  <si>
-    <t>27ASB25021397</t>
-  </si>
-  <si>
-    <t>0725ACH25000017</t>
-  </si>
-  <si>
-    <t>07ASB25037346</t>
-  </si>
-  <si>
-    <t>2725ACH25000058</t>
-  </si>
-  <si>
-    <t>27ASB25021523</t>
-  </si>
-  <si>
-    <t>TUKAR FAKTUR DI TGR</t>
+    <t>KP.SAMARINDA</t>
+  </si>
+  <si>
+    <t>18BSG25000014</t>
+  </si>
+  <si>
+    <t>DEPOSIT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
@@ -723,11 +707,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J88"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
@@ -816,7 +800,7 @@
         <v>19</v>
       </c>
       <c r="F4" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>20</v>
@@ -825,10 +809,10 @@
         <v>21</v>
       </c>
       <c r="I4" s="3">
-        <v>252525</v>
+        <v>1404930</v>
       </c>
       <c r="J4" s="3">
-        <v>252525</v>
+        <v>1404930</v>
       </c>
     </row>
     <row r="5" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -848,7 +832,7 @@
         <v>19</v>
       </c>
       <c r="F5" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>20</v>
@@ -857,10 +841,10 @@
         <v>21</v>
       </c>
       <c r="I5" s="3">
-        <v>426240</v>
+        <v>449550</v>
       </c>
       <c r="J5" s="3">
-        <v>426240</v>
+        <v>449550</v>
       </c>
     </row>
     <row r="6" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -880,7 +864,7 @@
         <v>19</v>
       </c>
       <c r="F6" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>20</v>
@@ -889,10 +873,10 @@
         <v>21</v>
       </c>
       <c r="I6" s="3">
-        <v>1007325</v>
+        <v>1410255</v>
       </c>
       <c r="J6" s="3">
-        <v>1007325</v>
+        <v>1410255</v>
       </c>
     </row>
     <row r="7" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
@@ -912,7 +896,7 @@
         <v>19</v>
       </c>
       <c r="F7" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>20</v>
@@ -921,30 +905,30 @@
         <v>21</v>
       </c>
       <c r="I7" s="3">
-        <v>3396600</v>
+        <v>1999998</v>
       </c>
       <c r="J7" s="3">
-        <v>3396600</v>
+        <v>1999998</v>
       </c>
     </row>
     <row r="8" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F8" s="4">
-        <v>45993</v>
+        <v>45966</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>20</v>
@@ -953,30 +937,30 @@
         <v>21</v>
       </c>
       <c r="I8" s="3">
-        <v>3468750</v>
+        <v>380512</v>
       </c>
       <c r="J8" s="3">
-        <v>3468750</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="9" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F9" s="4">
-        <v>45993</v>
+        <v>45966</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>20</v>
@@ -985,30 +969,30 @@
         <v>21</v>
       </c>
       <c r="I9" s="3">
-        <v>627705</v>
+        <v>197435</v>
       </c>
       <c r="J9" s="3">
-        <v>627705</v>
+        <v>195727</v>
       </c>
     </row>
     <row r="10" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="F10" s="4">
-        <v>45993</v>
+        <v>45966</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>20</v>
@@ -1017,30 +1001,30 @@
         <v>21</v>
       </c>
       <c r="I10" s="3">
-        <v>426240</v>
+        <v>197435</v>
       </c>
       <c r="J10" s="3">
-        <v>426240</v>
+        <v>37740</v>
       </c>
     </row>
     <row r="11" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F11" s="4">
-        <v>45993</v>
+        <v>45986</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>20</v>
@@ -1049,30 +1033,30 @@
         <v>21</v>
       </c>
       <c r="I11" s="3">
-        <v>321095</v>
+        <v>744028</v>
       </c>
       <c r="J11" s="3">
-        <v>321095</v>
+        <v>744028</v>
       </c>
     </row>
     <row r="12" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F12" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>20</v>
@@ -1081,30 +1065,30 @@
         <v>21</v>
       </c>
       <c r="I12" s="3">
-        <v>1497112</v>
+        <v>744028</v>
       </c>
       <c r="J12" s="3">
-        <v>1497112</v>
+        <v>744028</v>
       </c>
     </row>
     <row r="13" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F13" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>20</v>
@@ -1113,30 +1097,30 @@
         <v>21</v>
       </c>
       <c r="I13" s="3">
-        <v>460372</v>
+        <v>970748</v>
       </c>
       <c r="J13" s="3">
-        <v>460372</v>
+        <v>970748</v>
       </c>
     </row>
     <row r="14" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F14" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>20</v>
@@ -1145,30 +1129,30 @@
         <v>21</v>
       </c>
       <c r="I14" s="3">
-        <v>144044</v>
+        <v>744028</v>
       </c>
       <c r="J14" s="3">
-        <v>144044</v>
+        <v>744028</v>
       </c>
     </row>
     <row r="15" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F15" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>20</v>
@@ -1177,30 +1161,30 @@
         <v>21</v>
       </c>
       <c r="I15" s="3">
-        <v>36075</v>
+        <v>264335</v>
       </c>
       <c r="J15" s="3">
-        <v>36075</v>
+        <v>264335</v>
       </c>
     </row>
     <row r="16" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="F16" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>20</v>
@@ -1209,30 +1193,30 @@
         <v>21</v>
       </c>
       <c r="I16" s="3">
-        <v>201465</v>
+        <v>5991482</v>
       </c>
       <c r="J16" s="3">
-        <v>201465</v>
+        <v>574580</v>
       </c>
     </row>
     <row r="17" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F17" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>20</v>
@@ -1241,30 +1225,30 @@
         <v>21</v>
       </c>
       <c r="I17" s="3">
-        <v>902385</v>
+        <v>13059150</v>
       </c>
       <c r="J17" s="3">
-        <v>902385</v>
+        <v>277850</v>
       </c>
     </row>
     <row r="18" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F18" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>20</v>
@@ -1273,30 +1257,30 @@
         <v>21</v>
       </c>
       <c r="I18" s="3">
-        <v>166500</v>
+        <v>121367085</v>
       </c>
       <c r="J18" s="3">
-        <v>166500</v>
+        <v>24001142</v>
       </c>
     </row>
     <row r="19" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="F19" s="4">
-        <v>45993</v>
+        <v>46002</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>20</v>
@@ -1305,30 +1289,30 @@
         <v>21</v>
       </c>
       <c r="I19" s="3">
-        <v>2003550</v>
+        <v>1488057</v>
       </c>
       <c r="J19" s="3">
-        <v>2003550</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="20" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F20" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>20</v>
@@ -1337,30 +1321,30 @@
         <v>21</v>
       </c>
       <c r="I20" s="3">
-        <v>94905</v>
+        <v>744028</v>
       </c>
       <c r="J20" s="3">
-        <v>94905</v>
+        <v>744028</v>
       </c>
     </row>
     <row r="21" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F21" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>20</v>
@@ -1369,30 +1353,30 @@
         <v>21</v>
       </c>
       <c r="I21" s="3">
-        <v>208125</v>
+        <v>3235164</v>
       </c>
       <c r="J21" s="3">
-        <v>208125</v>
+        <v>3235164</v>
       </c>
     </row>
     <row r="22" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F22" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>20</v>
@@ -1401,30 +1385,30 @@
         <v>21</v>
       </c>
       <c r="I22" s="3">
-        <v>324675</v>
+        <v>744028</v>
       </c>
       <c r="J22" s="3">
-        <v>324675</v>
+        <v>744028</v>
       </c>
     </row>
     <row r="23" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F23" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>20</v>
@@ -1433,30 +1417,30 @@
         <v>21</v>
       </c>
       <c r="I23" s="3">
-        <v>94905</v>
+        <v>33688067</v>
       </c>
       <c r="J23" s="3">
-        <v>94905</v>
+        <v>33688067</v>
       </c>
     </row>
     <row r="24" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F24" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>20</v>
@@ -1465,30 +1449,30 @@
         <v>21</v>
       </c>
       <c r="I24" s="3">
-        <v>604395</v>
+        <v>197435</v>
       </c>
       <c r="J24" s="3">
-        <v>604395</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F25" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>20</v>
@@ -1497,30 +1481,30 @@
         <v>21</v>
       </c>
       <c r="I25" s="3">
-        <v>1254300</v>
+        <v>197435</v>
       </c>
       <c r="J25" s="3">
-        <v>1254300</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="26" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F26" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>20</v>
@@ -1529,30 +1513,30 @@
         <v>21</v>
       </c>
       <c r="I26" s="3">
-        <v>3330000</v>
+        <v>380512</v>
       </c>
       <c r="J26" s="3">
-        <v>3330000</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="27" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F27" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>20</v>
@@ -1561,30 +1545,30 @@
         <v>21</v>
       </c>
       <c r="I27" s="3">
-        <v>4162500</v>
+        <v>380512</v>
       </c>
       <c r="J27" s="3">
-        <v>4162500</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F28" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>20</v>
@@ -1593,30 +1577,30 @@
         <v>21</v>
       </c>
       <c r="I28" s="3">
-        <v>53537</v>
+        <v>402050</v>
       </c>
       <c r="J28" s="3">
-        <v>53537</v>
+        <v>402050</v>
       </c>
     </row>
     <row r="29" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F29" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>20</v>
@@ -1625,30 +1609,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="3">
-        <v>1491007</v>
+        <v>6634774</v>
       </c>
       <c r="J29" s="3">
-        <v>1491007</v>
+        <v>6634774</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F30" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>20</v>
@@ -1657,30 +1641,30 @@
         <v>21</v>
       </c>
       <c r="I30" s="3">
-        <v>162504</v>
+        <v>2095176</v>
       </c>
       <c r="J30" s="3">
-        <v>162504</v>
+        <v>2095176</v>
       </c>
     </row>
     <row r="31" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F31" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>20</v>
@@ -1689,30 +1673,30 @@
         <v>21</v>
       </c>
       <c r="I31" s="3">
-        <v>453550</v>
+        <v>17809137</v>
       </c>
       <c r="J31" s="3">
-        <v>453550</v>
+        <v>17809137</v>
       </c>
     </row>
     <row r="32" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F32" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>20</v>
@@ -1721,30 +1705,30 @@
         <v>21</v>
       </c>
       <c r="I32" s="3">
-        <v>557308</v>
+        <v>380512</v>
       </c>
       <c r="J32" s="3">
-        <v>557308</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="33" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F33" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>20</v>
@@ -1753,30 +1737,30 @@
         <v>21</v>
       </c>
       <c r="I33" s="3">
-        <v>201465</v>
+        <v>577948</v>
       </c>
       <c r="J33" s="3">
-        <v>201465</v>
+        <v>577948</v>
       </c>
     </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F34" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>20</v>
@@ -1785,30 +1769,30 @@
         <v>21</v>
       </c>
       <c r="I34" s="3">
-        <v>2278830</v>
+        <v>197435</v>
       </c>
       <c r="J34" s="3">
-        <v>2278830</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="35" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F35" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>20</v>
@@ -1817,30 +1801,30 @@
         <v>21</v>
       </c>
       <c r="I35" s="3">
-        <v>55444</v>
+        <v>6285593</v>
       </c>
       <c r="J35" s="3">
-        <v>55444</v>
+        <v>6285593</v>
       </c>
     </row>
     <row r="36" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F36" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>20</v>
@@ -1849,30 +1833,30 @@
         <v>21</v>
       </c>
       <c r="I36" s="3">
-        <v>158175</v>
+        <v>1056152</v>
       </c>
       <c r="J36" s="3">
-        <v>158175</v>
+        <v>1056152</v>
       </c>
     </row>
     <row r="37" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F37" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>20</v>
@@ -1881,30 +1865,30 @@
         <v>21</v>
       </c>
       <c r="I37" s="3">
-        <v>31635</v>
+        <v>2095198</v>
       </c>
       <c r="J37" s="3">
-        <v>31635</v>
+        <v>2095198</v>
       </c>
     </row>
     <row r="38" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F38" s="4">
-        <v>45993</v>
+        <v>46000</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>20</v>
@@ -1913,30 +1897,30 @@
         <v>21</v>
       </c>
       <c r="I38" s="3">
-        <v>11721</v>
+        <v>402050</v>
       </c>
       <c r="J38" s="3">
-        <v>11721</v>
+        <v>402050</v>
       </c>
     </row>
     <row r="39" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F39" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>20</v>
@@ -1945,30 +1929,30 @@
         <v>21</v>
       </c>
       <c r="I39" s="3">
-        <v>213120</v>
+        <v>394871</v>
       </c>
       <c r="J39" s="3">
-        <v>213120</v>
+        <v>394871</v>
       </c>
     </row>
     <row r="40" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F40" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>20</v>
@@ -1977,30 +1961,30 @@
         <v>21</v>
       </c>
       <c r="I40" s="3">
-        <v>454545</v>
+        <v>380512</v>
       </c>
       <c r="J40" s="3">
-        <v>454545</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="41" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F41" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>20</v>
@@ -2009,30 +1993,30 @@
         <v>21</v>
       </c>
       <c r="I41" s="3">
-        <v>117981</v>
+        <v>197435</v>
       </c>
       <c r="J41" s="3">
-        <v>117981</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="42" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F42" s="4">
-        <v>45993</v>
+        <v>46004</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>20</v>
@@ -2041,30 +2025,30 @@
         <v>21</v>
       </c>
       <c r="I42" s="3">
-        <v>948550</v>
+        <v>402050</v>
       </c>
       <c r="J42" s="3">
-        <v>948550</v>
+        <v>402050</v>
       </c>
     </row>
     <row r="43" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="F43" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>20</v>
@@ -2073,30 +2057,30 @@
         <v>21</v>
       </c>
       <c r="I43" s="3">
-        <v>1526250</v>
+        <v>1396408</v>
       </c>
       <c r="J43" s="3">
-        <v>1526250</v>
+        <v>1396408</v>
       </c>
     </row>
     <row r="44" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="F44" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>20</v>
@@ -2105,30 +2089,30 @@
         <v>21</v>
       </c>
       <c r="I44" s="3">
-        <v>4528800</v>
+        <v>2095198</v>
       </c>
       <c r="J44" s="3">
-        <v>4528800</v>
+        <v>2095198</v>
       </c>
     </row>
     <row r="45" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="F45" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>20</v>
@@ -2137,30 +2121,30 @@
         <v>21</v>
       </c>
       <c r="I45" s="3">
-        <v>213120</v>
+        <v>1762981</v>
       </c>
       <c r="J45" s="3">
-        <v>213120</v>
+        <v>1762981</v>
       </c>
     </row>
     <row r="46" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>63</v>
+        <v>99</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="F46" s="4">
-        <v>45993</v>
+        <v>46003</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>20</v>
@@ -2169,30 +2153,30 @@
         <v>21</v>
       </c>
       <c r="I46" s="3">
-        <v>805860</v>
+        <v>5121621</v>
       </c>
       <c r="J46" s="3">
-        <v>805860</v>
+        <v>5121621</v>
       </c>
     </row>
     <row r="47" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>19</v>
+        <v>98</v>
       </c>
       <c r="F47" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>20</v>
@@ -2201,30 +2185,30 @@
         <v>21</v>
       </c>
       <c r="I47" s="3">
-        <v>1192806</v>
+        <v>922211</v>
       </c>
       <c r="J47" s="3">
-        <v>1192806</v>
+        <v>922211</v>
       </c>
     </row>
     <row r="48" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F48" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>20</v>
@@ -2233,30 +2217,30 @@
         <v>21</v>
       </c>
       <c r="I48" s="3">
-        <v>266400</v>
+        <v>3164427</v>
       </c>
       <c r="J48" s="3">
-        <v>266400</v>
+        <v>3164427</v>
       </c>
     </row>
     <row r="49" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>66</v>
+        <v>103</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F49" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>20</v>
@@ -2265,30 +2249,30 @@
         <v>21</v>
       </c>
       <c r="I49" s="3">
-        <v>72150</v>
+        <v>1056153</v>
       </c>
       <c r="J49" s="3">
-        <v>72150</v>
+        <v>1056153</v>
       </c>
     </row>
     <row r="50" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F50" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>20</v>
@@ -2297,30 +2281,30 @@
         <v>21</v>
       </c>
       <c r="I50" s="3">
-        <v>201465</v>
+        <v>6634806</v>
       </c>
       <c r="J50" s="3">
-        <v>201465</v>
+        <v>6634806</v>
       </c>
     </row>
     <row r="51" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F51" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>20</v>
@@ -2329,30 +2313,30 @@
         <v>21</v>
       </c>
       <c r="I51" s="3">
-        <v>106893</v>
+        <v>197435</v>
       </c>
       <c r="J51" s="3">
-        <v>106893</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="52" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F52" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>20</v>
@@ -2361,30 +2345,30 @@
         <v>21</v>
       </c>
       <c r="I52" s="3">
-        <v>201465</v>
+        <v>12990324</v>
       </c>
       <c r="J52" s="3">
-        <v>201465</v>
+        <v>12990324</v>
       </c>
     </row>
     <row r="53" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>15</v>
+        <v>101</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F53" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>20</v>
@@ -2393,30 +2377,30 @@
         <v>21</v>
       </c>
       <c r="I53" s="3">
-        <v>1672215</v>
+        <v>12990324</v>
       </c>
       <c r="J53" s="3">
-        <v>1672215</v>
+        <v>12990324</v>
       </c>
     </row>
     <row r="54" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>72</v>
+        <v>108</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F54" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>20</v>
@@ -2425,30 +2409,30 @@
         <v>21</v>
       </c>
       <c r="I54" s="3">
-        <v>74925</v>
+        <v>402050</v>
       </c>
       <c r="J54" s="3">
-        <v>74925</v>
+        <v>402050</v>
       </c>
     </row>
     <row r="55" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>74</v>
+        <v>109</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F55" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>20</v>
@@ -2457,30 +2441,30 @@
         <v>21</v>
       </c>
       <c r="I55" s="3">
-        <v>7002213</v>
+        <v>197435</v>
       </c>
       <c r="J55" s="3">
-        <v>7002213</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="56" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F56" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>20</v>
@@ -2489,30 +2473,30 @@
         <v>21</v>
       </c>
       <c r="I56" s="3">
-        <v>3312795</v>
+        <v>2095198</v>
       </c>
       <c r="J56" s="3">
-        <v>3312795</v>
+        <v>2095198</v>
       </c>
     </row>
     <row r="57" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F57" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>20</v>
@@ -2521,30 +2505,30 @@
         <v>21</v>
       </c>
       <c r="I57" s="3">
-        <v>569430</v>
+        <v>2095198</v>
       </c>
       <c r="J57" s="3">
-        <v>569430</v>
+        <v>2095198</v>
       </c>
     </row>
     <row r="58" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F58" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>20</v>
@@ -2553,30 +2537,30 @@
         <v>21</v>
       </c>
       <c r="I58" s="3">
-        <v>31635</v>
+        <v>1056153</v>
       </c>
       <c r="J58" s="3">
-        <v>31635</v>
+        <v>1056153</v>
       </c>
     </row>
     <row r="59" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="F59" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>20</v>
@@ -2585,30 +2569,30 @@
         <v>21</v>
       </c>
       <c r="I59" s="3">
-        <v>497002</v>
+        <v>744028</v>
       </c>
       <c r="J59" s="3">
-        <v>497002</v>
+        <v>744028</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F60" s="4">
-        <v>45966</v>
+        <v>46006</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>20</v>
@@ -2617,30 +2601,30 @@
         <v>21</v>
       </c>
       <c r="I60" s="3">
-        <v>380512</v>
+        <v>2082488</v>
       </c>
       <c r="J60" s="3">
-        <v>380512</v>
+        <v>2082488</v>
       </c>
     </row>
     <row r="61" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>85</v>
+        <v>115</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F61" s="4">
-        <v>45966</v>
+        <v>46006</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>20</v>
@@ -2649,30 +2633,30 @@
         <v>21</v>
       </c>
       <c r="I61" s="3">
-        <v>197435</v>
+        <v>380512</v>
       </c>
       <c r="J61" s="3">
-        <v>195727</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="62" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="F62" s="4">
-        <v>45966</v>
+        <v>46006</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>20</v>
@@ -2681,30 +2665,30 @@
         <v>21</v>
       </c>
       <c r="I62" s="3">
-        <v>380512</v>
+        <v>402050</v>
       </c>
       <c r="J62" s="3">
-        <v>33504</v>
+        <v>402050</v>
       </c>
     </row>
     <row r="63" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="F63" s="4">
-        <v>45986</v>
+        <v>46006</v>
       </c>
       <c r="G63" s="3" t="s">
         <v>20</v>
@@ -2713,30 +2697,30 @@
         <v>21</v>
       </c>
       <c r="I63" s="3">
-        <v>2095198</v>
+        <v>323112829</v>
       </c>
       <c r="J63" s="3">
-        <v>489596</v>
+        <v>323112829</v>
       </c>
     </row>
     <row r="64" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F64" s="4">
-        <v>45966</v>
+        <v>46006</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>20</v>
@@ -2748,27 +2732,27 @@
         <v>197435</v>
       </c>
       <c r="J64" s="3">
-        <v>37740</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="65" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>94</v>
+        <v>119</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="F65" s="4">
-        <v>45992</v>
+        <v>46006</v>
       </c>
       <c r="G65" s="3" t="s">
         <v>20</v>
@@ -2777,30 +2761,30 @@
         <v>21</v>
       </c>
       <c r="I65" s="3">
-        <v>706826</v>
+        <v>380512</v>
       </c>
       <c r="J65" s="3">
-        <v>82450</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="66" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F66" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>20</v>
@@ -2809,30 +2793,30 @@
         <v>21</v>
       </c>
       <c r="I66" s="3">
-        <v>897083</v>
+        <v>197435</v>
       </c>
       <c r="J66" s="3">
-        <v>897083</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="67" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F67" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G67" s="3" t="s">
         <v>20</v>
@@ -2841,30 +2825,30 @@
         <v>21</v>
       </c>
       <c r="I67" s="3">
-        <v>607392</v>
+        <v>922211</v>
       </c>
       <c r="J67" s="3">
-        <v>607392</v>
+        <v>922211</v>
       </c>
     </row>
     <row r="68" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F68" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G68" s="3" t="s">
         <v>20</v>
@@ -2873,30 +2857,30 @@
         <v>21</v>
       </c>
       <c r="I68" s="3">
-        <v>2838067</v>
+        <v>380512</v>
       </c>
       <c r="J68" s="3">
-        <v>2838067</v>
+        <v>380512</v>
       </c>
     </row>
     <row r="69" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="F69" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G69" s="3" t="s">
         <v>20</v>
@@ -2905,30 +2889,30 @@
         <v>21</v>
       </c>
       <c r="I69" s="3">
-        <v>491508</v>
+        <v>2444410</v>
       </c>
       <c r="J69" s="3">
-        <v>491508</v>
+        <v>2444410</v>
       </c>
     </row>
     <row r="70" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F70" s="4">
-        <v>45986</v>
+        <v>46006</v>
       </c>
       <c r="G70" s="3" t="s">
         <v>20</v>
@@ -2937,30 +2921,30 @@
         <v>21</v>
       </c>
       <c r="I70" s="3">
-        <v>744028</v>
+        <v>197435</v>
       </c>
       <c r="J70" s="3">
-        <v>744028</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="71" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A71" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="F71" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G71" s="3" t="s">
         <v>20</v>
@@ -2969,30 +2953,30 @@
         <v>21</v>
       </c>
       <c r="I71" s="3">
-        <v>15244365</v>
+        <v>197435</v>
       </c>
       <c r="J71" s="3">
-        <v>14737723</v>
+        <v>197435</v>
       </c>
     </row>
     <row r="72" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>112</v>
+        <v>18</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>108</v>
+        <v>27</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="F72" s="4">
-        <v>45988</v>
+        <v>46006</v>
       </c>
       <c r="G72" s="3" t="s">
         <v>20</v>
@@ -3001,30 +2985,30 @@
         <v>21</v>
       </c>
       <c r="I72" s="3">
-        <v>270004</v>
+        <v>7517572</v>
       </c>
       <c r="J72" s="3">
-        <v>100004</v>
+        <v>7517572</v>
       </c>
     </row>
     <row r="73" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="F73" s="4">
-        <v>45988</v>
+        <v>45997</v>
       </c>
       <c r="G73" s="3" t="s">
         <v>20</v>
@@ -3033,30 +3017,30 @@
         <v>21</v>
       </c>
       <c r="I73" s="3">
-        <v>261008</v>
+        <v>3215096</v>
       </c>
       <c r="J73" s="3">
-        <v>75000</v>
+        <v>208092</v>
       </c>
     </row>
     <row r="74" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="F74" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G74" s="3" t="s">
         <v>20</v>
@@ -3065,458 +3049,42 @@
         <v>21</v>
       </c>
       <c r="I74" s="3">
-        <v>197435</v>
+        <v>1476300</v>
       </c>
       <c r="J74" s="3">
-        <v>197435</v>
+        <v>1476300</v>
       </c>
     </row>
     <row r="75" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F75" s="4">
-        <v>45993</v>
+        <v>46006</v>
       </c>
       <c r="G75" s="3" t="s">
         <v>20</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>21</v>
+        <v>138</v>
       </c>
       <c r="I75" s="3">
-        <v>979999</v>
+        <v>-1476300</v>
       </c>
       <c r="J75" s="3">
-        <v>979999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A76" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F76" s="4">
-        <v>45993</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I76" s="3">
-        <v>197435</v>
-      </c>
-      <c r="J76" s="3">
-        <v>197435</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F77" s="4">
-        <v>45992</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I77" s="3">
-        <v>1916921</v>
-      </c>
-      <c r="J77" s="3">
-        <v>1916921</v>
-      </c>
-    </row>
-    <row r="78" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A78" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F78" s="4">
-        <v>45992</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I78" s="3">
-        <v>380512</v>
-      </c>
-      <c r="J78" s="3">
-        <v>380512</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A79" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="F79" s="4">
-        <v>45992</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79" s="3">
-        <v>1474407</v>
-      </c>
-      <c r="J79" s="3">
-        <v>1474407</v>
-      </c>
-    </row>
-    <row r="80" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A80" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F80" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I80" s="3">
-        <v>599486</v>
-      </c>
-      <c r="J80" s="3">
-        <v>599486</v>
-      </c>
-    </row>
-    <row r="81" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A81" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F81" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I81" s="3">
-        <v>380512</v>
-      </c>
-      <c r="J81" s="3">
-        <v>380512</v>
-      </c>
-    </row>
-    <row r="82" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A82" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F82" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I82" s="3">
-        <v>706826</v>
-      </c>
-      <c r="J82" s="3">
-        <v>706826</v>
-      </c>
-    </row>
-    <row r="83" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F83" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4190395</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4190395</v>
-      </c>
-    </row>
-    <row r="84" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A84" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C84" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F84" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I84" s="3">
-        <v>12990219</v>
-      </c>
-      <c r="J84" s="3">
-        <v>12990219</v>
-      </c>
-    </row>
-    <row r="85" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A85" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C85" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F85" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I85" s="3">
-        <v>380512</v>
-      </c>
-      <c r="J85" s="3">
-        <v>380512</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A86" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C86" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F86" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I86" s="3">
-        <v>197435</v>
-      </c>
-      <c r="J86" s="3">
-        <v>197435</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A87" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C87" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="4">
-        <v>45989</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I87" s="3">
-        <v>2020014</v>
-      </c>
-      <c r="J87" s="3">
-        <v>2020014</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" s="3" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A88" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="F88" s="4">
-        <v>45990</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I88" s="3">
-        <v>532800</v>
-      </c>
-      <c r="J88" s="3">
-        <v>532800</v>
+        <v>-1476300</v>
       </c>
     </row>
   </sheetData>
